--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -1,22 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanahjansen/Documents/GitHub/appliedepidata/inst/extdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A071735-C90B-7A4F-9076-CE48082E0980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-37800" yWindow="780" windowWidth="35640" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="184">
   <si>
     <t>name</t>
   </si>
@@ -87,7 +103,7 @@
     <t>subnational</t>
   </si>
   <si>
-    <t xml:space="preserve">acute jaundice syndrome</t>
+    <t>acute jaundice syndrome</t>
   </si>
   <si>
     <t>outbreak</t>
@@ -96,13 +112,13 @@
     <t>no</t>
   </si>
   <si>
-    <t xml:space="preserve">Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
+    <t>Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
   </si>
   <si>
     <t>sitrep_walkthroughs</t>
   </si>
   <si>
-    <t xml:space="preserve">CC by-NC-SA 4.0</t>
+    <t>CC by-NC-SA 4.0</t>
   </si>
   <si>
     <t>AJS_AmTiman_population</t>
@@ -111,7 +127,7 @@
     <t>population</t>
   </si>
   <si>
-    <t xml:space="preserve">Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t>Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Blocksshape</t>
@@ -123,13 +139,13 @@
     <t>zip</t>
   </si>
   <si>
-    <t xml:space="preserve">Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t>Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Quartiersshape</t>
   </si>
   <si>
-    <t xml:space="preserve">Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t>Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>mortality_survey_data</t>
@@ -147,7 +163,7 @@
     <t>yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Fake data for a mortality survey</t>
+    <t>Fake data for a mortality survey</t>
   </si>
   <si>
     <t>gpl3</t>
@@ -159,7 +175,7 @@
     <t>dictionary</t>
   </si>
   <si>
-    <t xml:space="preserve">Fake data dictionary for a mortality survey</t>
+    <t>Fake data dictionary for a mortality survey</t>
   </si>
   <si>
     <t>franglais_AJS_AmTiman</t>
@@ -168,7 +184,7 @@
     <t>fr</t>
   </si>
   <si>
-    <t xml:space="preserve">quelque chose en francais - oui oui</t>
+    <t>quelque chose en francais - oui oui</t>
   </si>
   <si>
     <t>fulton_data</t>
@@ -180,7 +196,7 @@
     <t>covid-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Jittered COVID-19 linelist data from Fulton County</t>
+    <t>Jittered COVID-19 linelist data from Fulton County</t>
   </si>
   <si>
     <t>case_studies</t>
@@ -210,7 +226,7 @@
     <t>mpox</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional mpox case linelist in five European countries</t>
+    <t>Fictional mpox case linelist in five European countries</t>
   </si>
   <si>
     <t>r_practical</t>
@@ -225,7 +241,7 @@
     <t>csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional cumulative mpox case counts in five European countries</t>
+    <t>Fictional cumulative mpox case counts in five European countries</t>
   </si>
   <si>
     <t>stegentira_data</t>
@@ -237,7 +253,7 @@
     <t>salmonella</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional linelist of salmonella outbreak in Stegen, Germany</t>
+    <t>Fictional linelist of salmonella outbreak in Stegen, Germany</t>
   </si>
   <si>
     <t>fluH7N9_China_2013</t>
@@ -252,7 +268,7 @@
     <t>influenza</t>
   </si>
   <si>
-    <t xml:space="preserve">Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
+    <t>Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
   </si>
   <si>
     <t>epirhandbook</t>
@@ -270,52 +286,52 @@
     <t>ebola</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_excel</t>
   </si>
   <si>
-    <t xml:space="preserve">Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_rds</t>
   </si>
   <si>
-    <t xml:space="preserve">R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>hospital_linelists</t>
   </si>
   <si>
-    <t xml:space="preserve">Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_with_adm3</t>
   </si>
   <si>
-    <t xml:space="preserve">Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>cleaning_dict</t>
   </si>
   <si>
-    <t xml:space="preserve">Short example cleaning dictionary for the raw linelist</t>
+    <t>Short example cleaning dictionary for the raw linelist</t>
   </si>
   <si>
     <t>sle_adm3</t>
   </si>
   <si>
-    <t xml:space="preserve">Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC by-IGO</t>
+    <t>Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
+  </si>
+  <si>
+    <t>CC by-IGO</t>
   </si>
   <si>
     <t>sle_admpop_adm3_2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
+    <t>Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
   </si>
   <si>
     <t>epinow_res</t>
@@ -324,7 +340,7 @@
     <t>other</t>
   </si>
   <si>
-    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>epinow_res_small</t>
@@ -333,7 +349,7 @@
     <t>generation_time</t>
   </si>
   <si>
-    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
+    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
   </si>
   <si>
     <t>incubation_period</t>
@@ -342,10 +358,10 @@
     <t>cases_clean</t>
   </si>
   <si>
-    <t xml:space="preserve">contact tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fictional case data for a generic disease to demonstrate contact tracing</t>
+    <t>contact tracing</t>
+  </si>
+  <si>
+    <t>Fictional case data for a generic disease to demonstrate contact tracing</t>
   </si>
   <si>
     <t>contacts_clean</t>
@@ -366,7 +382,7 @@
     <t>malaria</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional counts of malaria cases from Mozambique</t>
+    <t>Fictional counts of malaria cases from Mozambique</t>
   </si>
   <si>
     <t>malaria_facility_count_data</t>
@@ -390,25 +406,25 @@
     <t>surveillance</t>
   </si>
   <si>
-    <t xml:space="preserve">Next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t>Next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>sample_data_Shigella_tree</t>
   </si>
   <si>
-    <t xml:space="preserve">Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
+    <t>Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
   </si>
   <si>
     <t>Shigella_subtree_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t>Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>country_demographics</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional country demographic and mortality data to demonstrate standardisation</t>
+    <t>Fictional country demographic and mortality data to demonstrate standardisation</t>
   </si>
   <si>
     <t>country_demographics_2</t>
@@ -423,7 +439,7 @@
     <t>world_standard_population_by_sex</t>
   </si>
   <si>
-    <t xml:space="preserve">World “standard population” by sex</t>
+    <t>World “standard population” by sex</t>
   </si>
   <si>
     <t>OGL</t>
@@ -435,22 +451,22 @@
     <t>likert</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional likert data for demonstration purposes</t>
+    <t>Fictional likert data for demonstration purposes</t>
   </si>
   <si>
     <t>survey_data</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional data for a mortality survey</t>
+    <t>Fictional data for a mortality survey</t>
   </si>
   <si>
     <t>survey_dict</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional data dictionary for a mortality survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fictional population data for a mortality survey</t>
+    <t>Fictional data dictionary for a mortality survey</t>
+  </si>
+  <si>
+    <t>Fictional population data for a mortality survey</t>
   </si>
   <si>
     <t>campylobacter_germany</t>
@@ -459,7 +475,7 @@
     <t>campylobacter</t>
   </si>
   <si>
-    <t xml:space="preserve">Campylobacter surveillance data from Germany</t>
+    <t>Campylobacter surveillance data from Germany</t>
   </si>
   <si>
     <t>germany_weather</t>
@@ -468,7 +484,7 @@
     <t>weather</t>
   </si>
   <si>
-    <t xml:space="preserve">Weather data for Germany from 2001-2011</t>
+    <t>Weather data for Germany from 2001-2011</t>
   </si>
   <si>
     <t>multidisease_tests</t>
@@ -477,7 +493,7 @@
     <t>multidisease</t>
   </si>
   <si>
-    <t xml:space="preserve">Test results for notifiable diseases reported in Feveria in 2024</t>
+    <t>Test results for notifiable diseases reported in Feveria in 2024</t>
   </si>
   <si>
     <t>multidisease_surveillance</t>
@@ -486,7 +502,7 @@
     <t>multidisease_notifications</t>
   </si>
   <si>
-    <t xml:space="preserve">Notifiable disease surveillance data in Feveria in 2024</t>
+    <t>Notifiable disease surveillance data in Feveria in 2024</t>
   </si>
   <si>
     <t>multi_maladies_notifications</t>
@@ -519,61 +535,95 @@
     <t>cholera</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 25 May 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qmd, intror</t>
+    <t>Clean cholera surveillance data for Viraland, 25 May 2021</t>
+  </si>
+  <si>
+    <t>qmd, intror</t>
   </si>
   <si>
     <t>viraland_cholera_20210617_linelist</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 17 June 2021</t>
+    <t>Clean cholera surveillance data for Viraland, 17 June 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 21 July 2021</t>
+    <t>Clean cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist_raw</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw cholera surveillance data for Viraland, 21 July 2021</t>
+    <t>Raw cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_labs</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw cholera lab data for Viraland, 21 July 2021</t>
+    <t>Raw cholera lab data for Viraland, 21 July 2021</t>
+  </si>
+  <si>
+    <t>feveriosis_main</t>
+  </si>
+  <si>
+    <t>Fake endemic vector-borne disease in Feveria 2025-26</t>
+  </si>
+  <si>
+    <t>feveriosis_surveillance</t>
+  </si>
+  <si>
+    <t>feveriosis_recent</t>
+  </si>
+  <si>
+    <t>Fake endemic vector-borne disease in Feveria 2025-27</t>
+  </si>
+  <si>
+    <t>CC by-NC-SA 4.1</t>
+  </si>
+  <si>
+    <t>feveriosis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.500000"/>
+      <sz val="11.5"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -586,31 +636,63 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="2"/>
+          <bgColor indexed="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -623,291 +705,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -1110,29 +909,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="44.26171875"/>
-    <col customWidth="1" min="2" max="2" width="10.3125"/>
+    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="3" width="9"/>
-    <col bestFit="1" customWidth="1" min="4" max="5" width="12.15625"/>
-    <col bestFit="1" min="8" max="8" width="10.68359375"/>
-    <col bestFit="1" min="9" max="9" width="22.47265625"/>
-    <col customWidth="1" min="10" max="11" width="11.15625"/>
-    <col customWidth="1" min="12" max="12" width="5.68359375"/>
-    <col bestFit="1" min="13" max="13" width="10.47265625"/>
-    <col bestFit="1" min="14" max="14" width="18.15625"/>
-    <col bestFit="1" min="15" max="15" width="14.3125"/>
-    <col bestFit="1" min="16" max="16" width="39.68359375"/>
-    <col bestFit="1" min="17" max="17" width="67.47265625"/>
+    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1"/>
+    <col min="14" max="14" width="18.1640625" bestFit="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1"/>
+    <col min="16" max="16" width="39.6640625" bestFit="1"/>
+    <col min="17" max="17" width="67.5" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.550000000000001" customHeight="1">
+    <row r="1" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,7 +986,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1232,15 +1033,15 @@
         <v>28</v>
       </c>
       <c r="P2" t="str">
-        <f t="shared" ref="P2:P9" si="0">_xlfn.CONCAT(SUBSTITUTE(I2," ",""),"_",J2,"_",G2,"_",L2)</f>
+        <f>CONCATENATE(SUBSTITUTE(I2," ",""),"_",J2,"_",G2,"_",L2)</f>
         <v>acutejaundicesyndrome_outbreak_tcd_2016</v>
       </c>
       <c r="Q2" t="str">
-        <f t="shared" ref="Q2:Q33" si="1">_xlfn.CONCAT(P2,"_",B2,"_",D2,"_",E2)</f>
+        <f>CONCATENATE(P2,"_",B2,"_",D2,"_",E2)</f>
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1287,15 +1088,15 @@
         <v>28</v>
       </c>
       <c r="P3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="P3:P62" si="0">CONCATENATE(SUBSTITUTE(I3," ",""),"_",J3,"_",G3,"_",L3)</f>
         <v>acutejaundicesyndrome_outbreak_tcd_2016</v>
       </c>
       <c r="Q3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="Q3:Q62" si="1">CONCATENATE(P3,"_",B3,"_",D3,"_",E3)</f>
         <v>acutejaundicesyndrome_outbreak_tcd_2016_population_1_1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1350,7 +1151,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_1_1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1405,7 +1206,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_2_1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1460,7 +1261,7 @@
         <v>mortality_survey_zzz_2021_survey_1_1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1515,7 +1316,7 @@
         <v>mortality_survey_zzz_2021_dictionary_1_1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1570,7 +1371,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1625,7 +1426,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1672,7 +1473,7 @@
         <v>28</v>
       </c>
       <c r="P10" t="str">
-        <f t="shared" ref="P10:P60" si="2">_xlfn.CONCAT(SUBSTITUTE(I10," ",""),"_",J10,"_",G10,"_",L10)</f>
+        <f t="shared" si="0"/>
         <v>covid-19_outbreak_usa_2020</v>
       </c>
       <c r="Q10" t="str">
@@ -1680,7 +1481,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1727,7 +1528,7 @@
         <v>28</v>
       </c>
       <c r="P11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>covid-19_outbreak_usa_2020</v>
       </c>
       <c r="Q11" t="str">
@@ -1735,7 +1536,7 @@
         <v>covid-19_outbreak_usa_2020_population_1_1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1782,7 +1583,7 @@
         <v>28</v>
       </c>
       <c r="P12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mpox_outbreak_eue_2022</v>
       </c>
       <c r="Q12" t="str">
@@ -1790,7 +1591,7 @@
         <v>mpox_outbreak_eue_2022_linelist_1_1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1837,7 +1638,7 @@
         <v>28</v>
       </c>
       <c r="P13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mpox_outbreak_eue_2022</v>
       </c>
       <c r="Q13" t="str">
@@ -1845,7 +1646,7 @@
         <v>mpox_outbreak_eue_2022_aggregate_1_1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1892,7 +1693,7 @@
         <v>28</v>
       </c>
       <c r="P14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>salmonella_outbreak_deu_1998</v>
       </c>
       <c r="Q14" t="str">
@@ -1900,7 +1701,7 @@
         <v>salmonella_outbreak_deu_1998_linelist_1_1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1947,7 +1748,7 @@
         <v>80</v>
       </c>
       <c r="P15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>influenza_outbreak_chn_2013</v>
       </c>
       <c r="Q15" t="str">
@@ -1955,7 +1756,7 @@
         <v>influenza_outbreak_chn_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -2002,7 +1803,7 @@
         <v>80</v>
       </c>
       <c r="P16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q16" t="str">
@@ -2010,7 +1811,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -2057,7 +1858,7 @@
         <v>80</v>
       </c>
       <c r="P17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q17" t="str">
@@ -2065,7 +1866,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -2112,7 +1913,7 @@
         <v>80</v>
       </c>
       <c r="P18" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q18" t="str">
@@ -2120,7 +1921,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_3</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -2167,7 +1968,7 @@
         <v>80</v>
       </c>
       <c r="P19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q19" t="str">
@@ -2175,7 +1976,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_4</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -2222,7 +2023,7 @@
         <v>80</v>
       </c>
       <c r="P20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q20" t="str">
@@ -2230,7 +2031,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -2277,7 +2078,7 @@
         <v>80</v>
       </c>
       <c r="P21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q21" t="str">
@@ -2285,7 +2086,7 @@
         <v>ebola_outbreak_sle_2014_dictionary_1_1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -2332,7 +2133,7 @@
         <v>97</v>
       </c>
       <c r="P22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q22" t="str">
@@ -2340,7 +2141,7 @@
         <v>ebola_outbreak_sle_2014_shape_1_1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -2387,7 +2188,7 @@
         <v>97</v>
       </c>
       <c r="P23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2020</v>
       </c>
       <c r="Q23" t="str">
@@ -2395,7 +2196,7 @@
         <v>ebola_outbreak_sle_2020_population_1_1</v>
       </c>
     </row>
-    <row r="24" ht="15.75">
+    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -2442,7 +2243,7 @@
         <v>80</v>
       </c>
       <c r="P24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q24" t="str">
@@ -2450,7 +2251,7 @@
         <v>ebola_outbreak_sle_2014_other_1_1</v>
       </c>
     </row>
-    <row r="25" ht="15.75">
+    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>103</v>
       </c>
@@ -2497,7 +2298,7 @@
         <v>80</v>
       </c>
       <c r="P25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q25" t="str">
@@ -2505,7 +2306,7 @@
         <v>ebola_outbreak_sle_2014_other_2_1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -2552,7 +2353,7 @@
         <v>80</v>
       </c>
       <c r="P26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q26" t="str">
@@ -2560,7 +2361,7 @@
         <v>ebola_outbreak_sle_2014_other_3_1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -2607,7 +2408,7 @@
         <v>80</v>
       </c>
       <c r="P27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>ebola_outbreak_sle_2014</v>
       </c>
       <c r="Q27" t="str">
@@ -2615,7 +2416,7 @@
         <v>ebola_outbreak_sle_2014_other_4_1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -2662,7 +2463,7 @@
         <v>44</v>
       </c>
       <c r="P28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>contacttracing_outbreak_zzz_2020</v>
       </c>
       <c r="Q28" t="str">
@@ -2670,7 +2471,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -2717,7 +2518,7 @@
         <v>44</v>
       </c>
       <c r="P29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>contacttracing_outbreak_zzz_2020</v>
       </c>
       <c r="Q29" t="str">
@@ -2725,7 +2526,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_2_1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -2772,7 +2573,7 @@
         <v>44</v>
       </c>
       <c r="P30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>contacttracing_outbreak_zzz_2020</v>
       </c>
       <c r="Q30" t="str">
@@ -2780,7 +2581,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_3_1</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -2827,7 +2628,7 @@
         <v>44</v>
       </c>
       <c r="P31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>contacttracing_outbreak_zzz_2020</v>
       </c>
       <c r="Q31" t="str">
@@ -2835,7 +2636,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_4_1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -2882,7 +2683,7 @@
         <v>28</v>
       </c>
       <c r="P32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>malaria_outbreak_moz_2019</v>
       </c>
       <c r="Q32" t="str">
@@ -2890,7 +2691,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -2937,7 +2738,7 @@
         <v>28</v>
       </c>
       <c r="P33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>malaria_outbreak_moz_2019</v>
       </c>
       <c r="Q33" t="str">
@@ -2945,7 +2746,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -2992,15 +2793,15 @@
         <v>28</v>
       </c>
       <c r="P34" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>shigella_surveillance_bel_2013</v>
       </c>
       <c r="Q34" t="str">
-        <f t="shared" ref="Q34:Q65" si="3">_xlfn.CONCAT(P34,"_",B34,"_",D34,"_",E34)</f>
+        <f t="shared" si="1"/>
         <v>shigella_surveillance_bel_2013_sequencing_1_1</v>
       </c>
     </row>
-    <row r="35" ht="15.550000000000001" customHeight="1">
+    <row r="35" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -3047,15 +2848,15 @@
         <v>28</v>
       </c>
       <c r="P35" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>shigella_surveillance_bel_2013</v>
       </c>
       <c r="Q35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>shigella_surveillance_bel_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>127</v>
       </c>
@@ -3102,15 +2903,15 @@
         <v>28</v>
       </c>
       <c r="P36" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>shigella_surveillance_bel_2013</v>
       </c>
       <c r="Q36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>shigella_surveillance_bel_2013_sequencing_1_2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -3157,15 +2958,15 @@
         <v>28</v>
       </c>
       <c r="P37" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_surveillance_zzz_2020</v>
       </c>
       <c r="Q37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_surveillance_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -3212,15 +3013,15 @@
         <v>28</v>
       </c>
       <c r="P38" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_surveillance_zzz_2020</v>
       </c>
       <c r="Q38" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_surveillance_zzz_2020_aggregate_2_1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>132</v>
       </c>
@@ -3267,15 +3068,15 @@
         <v>28</v>
       </c>
       <c r="P39" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_surveillance_zzz_2020</v>
       </c>
       <c r="Q39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_surveillance_zzz_2020_aggregate_3_1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>133</v>
       </c>
@@ -3322,15 +3123,15 @@
         <v>28</v>
       </c>
       <c r="P40" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_surveillance_zzz_2020</v>
       </c>
       <c r="Q40" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_surveillance_zzz_2020_aggregate_4_1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -3377,15 +3178,15 @@
         <v>136</v>
       </c>
       <c r="P41" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_surveillance_zzz_2020</v>
       </c>
       <c r="Q41" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_surveillance_zzz_2020_aggregate_5_1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3432,15 +3233,15 @@
         <v>28</v>
       </c>
       <c r="P42" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>likert_other_zzz_2020</v>
       </c>
       <c r="Q42" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>likert_other_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -3487,15 +3288,15 @@
         <v>44</v>
       </c>
       <c r="P43" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_survey_zzz_2021</v>
       </c>
       <c r="Q43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_survey_zzz_2021_survey_2_1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -3542,15 +3343,15 @@
         <v>44</v>
       </c>
       <c r="P44" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_survey_zzz_2021</v>
       </c>
       <c r="Q44" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_survey_zzz_2021_dictionary_2_1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -3597,15 +3398,15 @@
         <v>44</v>
       </c>
       <c r="P45" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>mortality_survey_zzz_2021</v>
       </c>
       <c r="Q45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>mortality_survey_zzz_2021_population_1_1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -3652,15 +3453,15 @@
         <v>44</v>
       </c>
       <c r="P46" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>campylobacter_surveillance_deu_2001</v>
       </c>
       <c r="Q46" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>campylobacter_surveillance_deu_2001_linelist_1_1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -3707,15 +3508,15 @@
         <v>44</v>
       </c>
       <c r="P47" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>weather_other_deu_2001</v>
       </c>
       <c r="Q47" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>weather_other_deu_2001_aggregate_1_1</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -3762,15 +3563,15 @@
         <v>28</v>
       </c>
       <c r="P48" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q48" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -3817,15 +3618,15 @@
         <v>28</v>
       </c>
       <c r="P49" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q49" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -3872,15 +3673,15 @@
         <v>28</v>
       </c>
       <c r="P50" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q50" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -3927,15 +3728,15 @@
         <v>28</v>
       </c>
       <c r="P51" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q51" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -3982,15 +3783,15 @@
         <v>28</v>
       </c>
       <c r="P52" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q52" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -4037,15 +3838,15 @@
         <v>28</v>
       </c>
       <c r="P53" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q53" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -4092,15 +3893,15 @@
         <v>28</v>
       </c>
       <c r="P54" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q54" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -4147,15 +3948,15 @@
         <v>28</v>
       </c>
       <c r="P55" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>multidisease_surveillance_zzz_2024</v>
       </c>
       <c r="Q55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -4202,15 +4003,15 @@
         <v>28</v>
       </c>
       <c r="P56" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>cholera_surveillance_zzz_2021</v>
       </c>
       <c r="Q56" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>cholera_surveillance_zzz_2021_linelist_1_3</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -4250,22 +4051,22 @@
       <c r="M57" t="s">
         <v>170</v>
       </c>
-      <c r="N57" s="4" t="s">
+      <c r="N57" t="s">
         <v>168</v>
       </c>
       <c r="O57" t="s">
         <v>28</v>
       </c>
       <c r="P57" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>cholera_surveillance_zzz_2021</v>
       </c>
       <c r="Q57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>cholera_surveillance_zzz_2021_linelist_1_4</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -4305,22 +4106,22 @@
       <c r="M58" t="s">
         <v>172</v>
       </c>
-      <c r="N58" s="4" t="s">
+      <c r="N58" t="s">
         <v>168</v>
       </c>
       <c r="O58" t="s">
         <v>28</v>
       </c>
       <c r="P58" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>cholera_surveillance_zzz_2021</v>
       </c>
       <c r="Q58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>cholera_surveillance_zzz_2021_linelist_1_1</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -4360,22 +4161,22 @@
       <c r="M59" t="s">
         <v>174</v>
       </c>
-      <c r="N59" s="4" t="s">
+      <c r="N59" t="s">
         <v>168</v>
       </c>
       <c r="O59" t="s">
         <v>28</v>
       </c>
       <c r="P59" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>cholera_surveillance_zzz_2021</v>
       </c>
       <c r="Q59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>cholera_surveillance_zzz_2021_linelist_1_2</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -4415,77 +4216,145 @@
       <c r="M60" t="s">
         <v>176</v>
       </c>
-      <c r="N60" s="4" t="s">
+      <c r="N60" t="s">
         <v>168</v>
       </c>
       <c r="O60" t="s">
         <v>28</v>
       </c>
       <c r="P60" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>cholera_surveillance_zzz_2021</v>
       </c>
       <c r="Q60" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>cholera_surveillance_zzz_2021_linelist_1_5</v>
       </c>
     </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H61" t="s">
+        <v>76</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61">
+        <v>2025</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="O61" t="s">
+        <v>28</v>
+      </c>
+      <c r="P61" t="str">
+        <f t="shared" si="0"/>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q61" t="str">
+        <f t="shared" si="1"/>
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H62" t="s">
+        <v>76</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62">
+        <v>2025</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="O62" t="s">
+        <v>182</v>
+      </c>
+      <c r="P62" t="str">
+        <f t="shared" si="0"/>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q62" t="str">
+        <f t="shared" si="1"/>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="3" id="{00DA006C-00CF-44EB-B19D-0047002000B9}">
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A1:A53 A56:A1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="4" id="{002A0088-0095-4F59-A247-0052005900F4}">
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{00F0009D-0044-498A-8203-005F00AF00AA}">
-            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G2:G300 K56:K60</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A53 A56:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K56:K62 G2:G300">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanahjansen/Documents/GitHub/appliedepidata/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A071735-C90B-7A4F-9076-CE48082E0980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF635EF5-22EF-7041-BBB8-276C994C7A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37800" yWindow="780" windowWidth="35640" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="183">
   <si>
     <t>name</t>
   </si>
@@ -578,9 +578,6 @@
   </si>
   <si>
     <t>Fake endemic vector-borne disease in Feveria 2025-27</t>
-  </si>
-  <si>
-    <t>CC by-NC-SA 4.1</t>
   </si>
   <si>
     <t>feveriosis</t>
@@ -602,15 +599,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.5"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -646,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -656,7 +656,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4232,7 +4231,7 @@
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
+      <c r="A61" t="s">
         <v>177</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -4257,7 +4256,7 @@
         <v>76</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>123</v>
@@ -4287,7 +4286,7 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
+      <c r="A62" t="s">
         <v>180</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -4312,7 +4311,7 @@
         <v>76</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>123</v>
@@ -4329,8 +4328,8 @@
       <c r="N62" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="O62" t="s">
-        <v>182</v>
+      <c r="O62" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="P62" t="str">
         <f t="shared" si="0"/>
@@ -4349,7 +4348,7 @@
   <conditionalFormatting sqref="A25">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K56:K62 G2:G300">
+  <conditionalFormatting sqref="G2:G300 K56:K62">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</formula>
     </cfRule>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanahjansen/Documents/GitHub/appliedepidata/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF635EF5-22EF-7041-BBB8-276C994C7A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E96078-6B29-F744-B65D-81FD1DAC6F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37800" yWindow="780" windowWidth="35640" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34960" yWindow="1920" windowWidth="35640" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4244,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>20</v>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="1"/>
-        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_2</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
@@ -4299,7 +4299,7 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>20</v>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="Q62" t="str">
         <f t="shared" si="1"/>
-        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_2</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -1,38 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanahjansen/Documents/GitHub/appliedepidata/inst/extdata/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E96078-6B29-F744-B65D-81FD1DAC6F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34960" yWindow="1920" windowWidth="35640" windowHeight="18280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>name</t>
   </si>
@@ -103,7 +87,7 @@
     <t>subnational</t>
   </si>
   <si>
-    <t>acute jaundice syndrome</t>
+    <t xml:space="preserve">acute jaundice syndrome</t>
   </si>
   <si>
     <t>outbreak</t>
@@ -112,13 +96,13 @@
     <t>no</t>
   </si>
   <si>
-    <t>Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
+    <t xml:space="preserve">Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
   </si>
   <si>
     <t>sitrep_walkthroughs</t>
   </si>
   <si>
-    <t>CC by-NC-SA 4.0</t>
+    <t xml:space="preserve">CC by-NC-SA 4.0</t>
   </si>
   <si>
     <t>AJS_AmTiman_population</t>
@@ -127,7 +111,7 @@
     <t>population</t>
   </si>
   <si>
-    <t>Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t xml:space="preserve">Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Blocksshape</t>
@@ -139,13 +123,13 @@
     <t>zip</t>
   </si>
   <si>
-    <t>Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t xml:space="preserve">Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Quartiersshape</t>
   </si>
   <si>
-    <t>Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t xml:space="preserve">Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>mortality_survey_data</t>
@@ -163,7 +147,7 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Fake data for a mortality survey</t>
+    <t xml:space="preserve">Fake data for a mortality survey</t>
   </si>
   <si>
     <t>gpl3</t>
@@ -175,7 +159,7 @@
     <t>dictionary</t>
   </si>
   <si>
-    <t>Fake data dictionary for a mortality survey</t>
+    <t xml:space="preserve">Fake data dictionary for a mortality survey</t>
   </si>
   <si>
     <t>franglais_AJS_AmTiman</t>
@@ -184,7 +168,7 @@
     <t>fr</t>
   </si>
   <si>
-    <t>quelque chose en francais - oui oui</t>
+    <t xml:space="preserve">quelque chose en francais - oui oui</t>
   </si>
   <si>
     <t>fulton_data</t>
@@ -196,7 +180,7 @@
     <t>covid-19</t>
   </si>
   <si>
-    <t>Jittered COVID-19 linelist data from Fulton County</t>
+    <t xml:space="preserve">Jittered COVID-19 linelist data from Fulton County</t>
   </si>
   <si>
     <t>case_studies</t>
@@ -226,7 +210,7 @@
     <t>mpox</t>
   </si>
   <si>
-    <t>Fictional mpox case linelist in five European countries</t>
+    <t xml:space="preserve">Fictional mpox case linelist in five European countries</t>
   </si>
   <si>
     <t>r_practical</t>
@@ -241,7 +225,7 @@
     <t>csv</t>
   </si>
   <si>
-    <t>Fictional cumulative mpox case counts in five European countries</t>
+    <t xml:space="preserve">Fictional cumulative mpox case counts in five European countries</t>
   </si>
   <si>
     <t>stegentira_data</t>
@@ -253,7 +237,7 @@
     <t>salmonella</t>
   </si>
   <si>
-    <t>Fictional linelist of salmonella outbreak in Stegen, Germany</t>
+    <t xml:space="preserve">Fictional linelist of salmonella outbreak in Stegen, Germany</t>
   </si>
   <si>
     <t>fluH7N9_China_2013</t>
@@ -268,7 +252,7 @@
     <t>influenza</t>
   </si>
   <si>
-    <t>Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
+    <t xml:space="preserve">Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
   </si>
   <si>
     <t>epirhandbook</t>
@@ -286,52 +270,52 @@
     <t>ebola</t>
   </si>
   <si>
-    <t>Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_excel</t>
   </si>
   <si>
-    <t>Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_rds</t>
   </si>
   <si>
-    <t>R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>hospital_linelists</t>
   </si>
   <si>
-    <t>Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_with_adm3</t>
   </si>
   <si>
-    <t>Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>cleaning_dict</t>
   </si>
   <si>
-    <t>Short example cleaning dictionary for the raw linelist</t>
+    <t xml:space="preserve">Short example cleaning dictionary for the raw linelist</t>
   </si>
   <si>
     <t>sle_adm3</t>
   </si>
   <si>
-    <t>Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
-  </si>
-  <si>
-    <t>CC by-IGO</t>
+    <t xml:space="preserve">Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC by-IGO</t>
   </si>
   <si>
     <t>sle_admpop_adm3_2020</t>
   </si>
   <si>
-    <t>Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
+    <t xml:space="preserve">Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
   </si>
   <si>
     <t>epinow_res</t>
@@ -340,7 +324,7 @@
     <t>other</t>
   </si>
   <si>
-    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>epinow_res_small</t>
@@ -349,7 +333,7 @@
     <t>generation_time</t>
   </si>
   <si>
-    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
+    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
   </si>
   <si>
     <t>incubation_period</t>
@@ -358,10 +342,10 @@
     <t>cases_clean</t>
   </si>
   <si>
-    <t>contact tracing</t>
-  </si>
-  <si>
-    <t>Fictional case data for a generic disease to demonstrate contact tracing</t>
+    <t xml:space="preserve">contact tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictional case data for a generic disease to demonstrate contact tracing</t>
   </si>
   <si>
     <t>contacts_clean</t>
@@ -382,7 +366,7 @@
     <t>malaria</t>
   </si>
   <si>
-    <t>Fictional counts of malaria cases from Mozambique</t>
+    <t xml:space="preserve">Fictional counts of malaria cases from Mozambique</t>
   </si>
   <si>
     <t>malaria_facility_count_data</t>
@@ -406,25 +390,25 @@
     <t>surveillance</t>
   </si>
   <si>
-    <t>Next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t xml:space="preserve">Next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>sample_data_Shigella_tree</t>
   </si>
   <si>
-    <t>Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
+    <t xml:space="preserve">Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
   </si>
   <si>
     <t>Shigella_subtree_2</t>
   </si>
   <si>
-    <t>Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t xml:space="preserve">Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>country_demographics</t>
   </si>
   <si>
-    <t>Fictional country demographic and mortality data to demonstrate standardisation</t>
+    <t xml:space="preserve">Fictional country demographic and mortality data to demonstrate standardisation</t>
   </si>
   <si>
     <t>country_demographics_2</t>
@@ -439,7 +423,7 @@
     <t>world_standard_population_by_sex</t>
   </si>
   <si>
-    <t>World “standard population” by sex</t>
+    <t xml:space="preserve">World “standard population” by sex</t>
   </si>
   <si>
     <t>OGL</t>
@@ -451,22 +435,22 @@
     <t>likert</t>
   </si>
   <si>
-    <t>Fictional likert data for demonstration purposes</t>
+    <t xml:space="preserve">Fictional likert data for demonstration purposes</t>
   </si>
   <si>
     <t>survey_data</t>
   </si>
   <si>
-    <t>Fictional data for a mortality survey</t>
+    <t xml:space="preserve">Fictional data for a mortality survey</t>
   </si>
   <si>
     <t>survey_dict</t>
   </si>
   <si>
-    <t>Fictional data dictionary for a mortality survey</t>
-  </si>
-  <si>
-    <t>Fictional population data for a mortality survey</t>
+    <t xml:space="preserve">Fictional data dictionary for a mortality survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictional population data for a mortality survey</t>
   </si>
   <si>
     <t>campylobacter_germany</t>
@@ -475,7 +459,7 @@
     <t>campylobacter</t>
   </si>
   <si>
-    <t>Campylobacter surveillance data from Germany</t>
+    <t xml:space="preserve">Campylobacter surveillance data from Germany</t>
   </si>
   <si>
     <t>germany_weather</t>
@@ -484,7 +468,7 @@
     <t>weather</t>
   </si>
   <si>
-    <t>Weather data for Germany from 2001-2011</t>
+    <t xml:space="preserve">Weather data for Germany from 2001-2011</t>
   </si>
   <si>
     <t>multidisease_tests</t>
@@ -493,7 +477,7 @@
     <t>multidisease</t>
   </si>
   <si>
-    <t>Test results for notifiable diseases reported in Feveria in 2024</t>
+    <t xml:space="preserve">Test results for notifiable diseases reported in Feveria in 2024</t>
   </si>
   <si>
     <t>multidisease_surveillance</t>
@@ -502,7 +486,7 @@
     <t>multidisease_notifications</t>
   </si>
   <si>
-    <t>Notifiable disease surveillance data in Feveria in 2024</t>
+    <t xml:space="preserve">Notifiable disease surveillance data in Feveria in 2024</t>
   </si>
   <si>
     <t>multi_maladies_notifications</t>
@@ -535,40 +519,43 @@
     <t>cholera</t>
   </si>
   <si>
-    <t>Clean cholera surveillance data for Viraland, 25 May 2021</t>
-  </si>
-  <si>
-    <t>qmd, intror</t>
+    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 25 May 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qmd, intror</t>
   </si>
   <si>
     <t>viraland_cholera_20210617_linelist</t>
   </si>
   <si>
-    <t>Clean cholera surveillance data for Viraland, 17 June 2021</t>
+    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 17 June 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist</t>
   </si>
   <si>
-    <t>Clean cholera surveillance data for Viraland, 21 July 2021</t>
+    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist_raw</t>
   </si>
   <si>
-    <t>Raw cholera surveillance data for Viraland, 21 July 2021</t>
+    <t xml:space="preserve">Raw cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_labs</t>
   </si>
   <si>
-    <t>Raw cholera lab data for Viraland, 21 July 2021</t>
+    <t xml:space="preserve">Raw cholera lab data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>feveriosis_main</t>
   </si>
   <si>
-    <t>Fake endemic vector-borne disease in Feveria 2025-26</t>
+    <t>feveriosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fake endemic vector-borne disease in Feveria 2025-26</t>
   </si>
   <si>
     <t>feveriosis_surveillance</t>
@@ -577,53 +564,34 @@
     <t>feveriosis_recent</t>
   </si>
   <si>
-    <t>Fake endemic vector-borne disease in Feveria 2025-27</t>
-  </si>
-  <si>
-    <t>feveriosis</t>
+    <t xml:space="preserve">Fake endemic vector-borne disease in Feveria 2025-27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.5"/>
+      <sz val="11.500000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -636,62 +604,31 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="2"/>
-          <bgColor indexed="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -704,8 +641,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -908,31 +1128,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="44.33203125"/>
+    <col customWidth="1" min="2" max="2" width="10.33203125"/>
     <col min="3" max="3" width="9"/>
-    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" bestFit="1"/>
-    <col min="9" max="9" width="22.5" bestFit="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="10.5" bestFit="1"/>
-    <col min="14" max="14" width="18.1640625" bestFit="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1"/>
-    <col min="16" max="16" width="39.6640625" bestFit="1"/>
-    <col min="17" max="17" width="67.5" bestFit="1"/>
+    <col bestFit="1" customWidth="1" min="4" max="5" width="12.1640625"/>
+    <col bestFit="1" min="8" max="8" width="10.6640625"/>
+    <col bestFit="1" min="9" max="9" width="22.5"/>
+    <col customWidth="1" min="10" max="11" width="11.1640625"/>
+    <col customWidth="1" min="12" max="12" width="5.6640625"/>
+    <col bestFit="1" min="13" max="13" width="10.5"/>
+    <col bestFit="1" min="14" max="14" width="18.1640625"/>
+    <col bestFit="1" min="15" max="15" width="14.33203125"/>
+    <col bestFit="1" min="16" max="16" width="39.6640625"/>
+    <col bestFit="1" min="17" max="17" width="67.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +1203,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1032,15 +1250,15 @@
         <v>28</v>
       </c>
       <c r="P2" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I2," ",""),"_",J2,"_",G2,"_",L2)</f>
+        <f t="shared" ref="P2:P62" si="0">CONCATENATE(SUBSTITUTE(I2," ",""),"_",J2,"_",G2,"_",L2)</f>
         <v>acutejaundicesyndrome_outbreak_tcd_2016</v>
       </c>
       <c r="Q2" t="str">
-        <f>CONCATENATE(P2,"_",B2,"_",D2,"_",E2)</f>
+        <f t="shared" ref="Q2:Q62" si="1">CONCATENATE(P2,"_",B2,"_",D2,"_",E2)</f>
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1087,15 +1305,15 @@
         <v>28</v>
       </c>
       <c r="P3" t="str">
-        <f t="shared" ref="P3:P62" si="0">CONCATENATE(SUBSTITUTE(I3," ",""),"_",J3,"_",G3,"_",L3)</f>
+        <f t="shared" si="0"/>
         <v>acutejaundicesyndrome_outbreak_tcd_2016</v>
       </c>
       <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q62" si="1">CONCATENATE(P3,"_",B3,"_",D3,"_",E3)</f>
+        <f t="shared" si="1"/>
         <v>acutejaundicesyndrome_outbreak_tcd_2016_population_1_1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1150,7 +1368,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_1_1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1205,7 +1423,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_2_1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1260,7 +1478,7 @@
         <v>mortality_survey_zzz_2021_survey_1_1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1315,7 +1533,7 @@
         <v>mortality_survey_zzz_2021_dictionary_1_1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1370,7 +1588,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1425,7 +1643,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1480,7 +1698,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1535,7 +1753,7 @@
         <v>covid-19_outbreak_usa_2020_population_1_1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1590,7 +1808,7 @@
         <v>mpox_outbreak_eue_2022_linelist_1_1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1645,7 +1863,7 @@
         <v>mpox_outbreak_eue_2022_aggregate_1_1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1700,7 +1918,7 @@
         <v>salmonella_outbreak_deu_1998_linelist_1_1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1755,7 +1973,7 @@
         <v>influenza_outbreak_chn_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -1810,7 +2028,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -1865,7 +2083,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -1920,7 +2138,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -1975,7 +2193,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -2030,7 +2248,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -2085,7 +2303,7 @@
         <v>ebola_outbreak_sle_2014_dictionary_1_1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -2140,7 +2358,7 @@
         <v>ebola_outbreak_sle_2014_shape_1_1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -2195,7 +2413,7 @@
         <v>ebola_outbreak_sle_2020_population_1_1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" ht="15.75">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -2250,7 +2468,7 @@
         <v>ebola_outbreak_sle_2014_other_1_1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" ht="15.75">
       <c r="A25" s="2" t="s">
         <v>103</v>
       </c>
@@ -2305,7 +2523,7 @@
         <v>ebola_outbreak_sle_2014_other_2_1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -2360,7 +2578,7 @@
         <v>ebola_outbreak_sle_2014_other_3_1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -2415,7 +2633,7 @@
         <v>ebola_outbreak_sle_2014_other_4_1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -2470,7 +2688,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -2525,7 +2743,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_2_1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -2580,7 +2798,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_3_1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -2635,7 +2853,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_4_1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -2690,7 +2908,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -2745,7 +2963,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -2800,7 +3018,7 @@
         <v>shigella_surveillance_bel_2013_sequencing_1_1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="15.5" customHeight="1">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -2855,7 +3073,7 @@
         <v>shigella_surveillance_bel_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36" t="s">
         <v>127</v>
       </c>
@@ -2910,7 +3128,7 @@
         <v>shigella_surveillance_bel_2013_sequencing_1_2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -2965,7 +3183,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -3020,7 +3238,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_2_1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39" t="s">
         <v>132</v>
       </c>
@@ -3075,7 +3293,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_3_1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40" t="s">
         <v>133</v>
       </c>
@@ -3130,7 +3348,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_4_1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -3185,7 +3403,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_5_1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3240,7 +3458,7 @@
         <v>likert_other_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -3295,7 +3513,7 @@
         <v>mortality_survey_zzz_2021_survey_2_1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -3350,7 +3568,7 @@
         <v>mortality_survey_zzz_2021_dictionary_2_1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -3405,7 +3623,7 @@
         <v>mortality_survey_zzz_2021_population_1_1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -3460,7 +3678,7 @@
         <v>campylobacter_surveillance_deu_2001_linelist_1_1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -3515,7 +3733,7 @@
         <v>weather_other_deu_2001_aggregate_1_1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -3570,7 +3788,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -3625,7 +3843,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -3680,7 +3898,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -3735,7 +3953,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -3790,7 +4008,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -3845,7 +4063,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -3900,7 +4118,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -3955,7 +4173,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -4010,7 +4228,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -4065,7 +4283,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_4</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -4120,7 +4338,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -4175,7 +4393,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -4230,7 +4448,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="61">
       <c r="A61" t="s">
         <v>177</v>
       </c>
@@ -4244,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>20</v>
@@ -4256,7 +4474,7 @@
         <v>76</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>123</v>
@@ -4268,10 +4486,10 @@
         <v>2025</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O61" t="s">
         <v>28</v>
@@ -4282,12 +4500,12 @@
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="1"/>
-        <v>feveriosis_surveillance_zzz_2025_linelist_1_2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>18</v>
@@ -4299,7 +4517,7 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>20</v>
@@ -4311,7 +4529,7 @@
         <v>76</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>123</v>
@@ -4323,10 +4541,10 @@
         <v>2025</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O62" s="4" t="s">
         <v>28</v>
@@ -4337,23 +4555,65 @@
       </c>
       <c r="Q62" t="str">
         <f t="shared" si="1"/>
-        <v>feveriosis_surveillance_zzz_2025_linelist_2_2</v>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A53 A56:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G300 K56:K62">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{00F30094-00B0-4006-B3DA-002100A30031}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A1:A53 A56:A1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="4" id="{006000EA-00CE-4DA1-8999-009E004800A6}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{008E009D-00EE-46A3-984F-00500093008B}">
+            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="2"/>
+                  <bgColor indexed="2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G2:G300 K56:K62</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -1,22 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanahjansen/Documents/GitHub/appliedepidata/inst/extdata/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15CCCFF-45D0-AF4B-A094-AE47A658DD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="500" windowWidth="20960" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="183">
   <si>
     <t>name</t>
   </si>
@@ -87,7 +104,7 @@
     <t>subnational</t>
   </si>
   <si>
-    <t xml:space="preserve">acute jaundice syndrome</t>
+    <t>acute jaundice syndrome</t>
   </si>
   <si>
     <t>outbreak</t>
@@ -96,13 +113,13 @@
     <t>no</t>
   </si>
   <si>
-    <t xml:space="preserve">Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
+    <t>Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
   </si>
   <si>
     <t>sitrep_walkthroughs</t>
   </si>
   <si>
-    <t xml:space="preserve">CC by-NC-SA 4.0</t>
+    <t>CC by-NC-SA 4.0</t>
   </si>
   <si>
     <t>AJS_AmTiman_population</t>
@@ -111,7 +128,7 @@
     <t>population</t>
   </si>
   <si>
-    <t xml:space="preserve">Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t>Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Blocksshape</t>
@@ -123,13 +140,13 @@
     <t>zip</t>
   </si>
   <si>
-    <t xml:space="preserve">Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t>Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Quartiersshape</t>
   </si>
   <si>
-    <t xml:space="preserve">Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t>Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>mortality_survey_data</t>
@@ -147,7 +164,7 @@
     <t>yes</t>
   </si>
   <si>
-    <t xml:space="preserve">Fake data for a mortality survey</t>
+    <t>Fake data for a mortality survey</t>
   </si>
   <si>
     <t>gpl3</t>
@@ -159,7 +176,7 @@
     <t>dictionary</t>
   </si>
   <si>
-    <t xml:space="preserve">Fake data dictionary for a mortality survey</t>
+    <t>Fake data dictionary for a mortality survey</t>
   </si>
   <si>
     <t>franglais_AJS_AmTiman</t>
@@ -168,7 +185,7 @@
     <t>fr</t>
   </si>
   <si>
-    <t xml:space="preserve">quelque chose en francais - oui oui</t>
+    <t>quelque chose en francais - oui oui</t>
   </si>
   <si>
     <t>fulton_data</t>
@@ -180,7 +197,7 @@
     <t>covid-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Jittered COVID-19 linelist data from Fulton County</t>
+    <t>Jittered COVID-19 linelist data from Fulton County</t>
   </si>
   <si>
     <t>case_studies</t>
@@ -210,7 +227,7 @@
     <t>mpox</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional mpox case linelist in five European countries</t>
+    <t>Fictional mpox case linelist in five European countries</t>
   </si>
   <si>
     <t>r_practical</t>
@@ -225,7 +242,7 @@
     <t>csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional cumulative mpox case counts in five European countries</t>
+    <t>Fictional cumulative mpox case counts in five European countries</t>
   </si>
   <si>
     <t>stegentira_data</t>
@@ -237,7 +254,7 @@
     <t>salmonella</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional linelist of salmonella outbreak in Stegen, Germany</t>
+    <t>Fictional linelist of salmonella outbreak in Stegen, Germany</t>
   </si>
   <si>
     <t>fluH7N9_China_2013</t>
@@ -252,7 +269,7 @@
     <t>influenza</t>
   </si>
   <si>
-    <t xml:space="preserve">Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
+    <t>Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
   </si>
   <si>
     <t>epirhandbook</t>
@@ -270,52 +287,52 @@
     <t>ebola</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_excel</t>
   </si>
   <si>
-    <t xml:space="preserve">Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_rds</t>
   </si>
   <si>
-    <t xml:space="preserve">R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>hospital_linelists</t>
   </si>
   <si>
-    <t xml:space="preserve">Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_with_adm3</t>
   </si>
   <si>
-    <t xml:space="preserve">Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>cleaning_dict</t>
   </si>
   <si>
-    <t xml:space="preserve">Short example cleaning dictionary for the raw linelist</t>
+    <t>Short example cleaning dictionary for the raw linelist</t>
   </si>
   <si>
     <t>sle_adm3</t>
   </si>
   <si>
-    <t xml:space="preserve">Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC by-IGO</t>
+    <t>Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
+  </si>
+  <si>
+    <t>CC by-IGO</t>
   </si>
   <si>
     <t>sle_admpop_adm3_2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
+    <t>Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
   </si>
   <si>
     <t>epinow_res</t>
@@ -324,7 +341,7 @@
     <t>other</t>
   </si>
   <si>
-    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>epinow_res_small</t>
@@ -333,7 +350,7 @@
     <t>generation_time</t>
   </si>
   <si>
-    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
+    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
   </si>
   <si>
     <t>incubation_period</t>
@@ -342,10 +359,10 @@
     <t>cases_clean</t>
   </si>
   <si>
-    <t xml:space="preserve">contact tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fictional case data for a generic disease to demonstrate contact tracing</t>
+    <t>contact tracing</t>
+  </si>
+  <si>
+    <t>Fictional case data for a generic disease to demonstrate contact tracing</t>
   </si>
   <si>
     <t>contacts_clean</t>
@@ -366,7 +383,7 @@
     <t>malaria</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional counts of malaria cases from Mozambique</t>
+    <t>Fictional counts of malaria cases from Mozambique</t>
   </si>
   <si>
     <t>malaria_facility_count_data</t>
@@ -390,25 +407,25 @@
     <t>surveillance</t>
   </si>
   <si>
-    <t xml:space="preserve">Next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t>Next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>sample_data_Shigella_tree</t>
   </si>
   <si>
-    <t xml:space="preserve">Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
+    <t>Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
   </si>
   <si>
     <t>Shigella_subtree_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t>Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>country_demographics</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional country demographic and mortality data to demonstrate standardisation</t>
+    <t>Fictional country demographic and mortality data to demonstrate standardisation</t>
   </si>
   <si>
     <t>country_demographics_2</t>
@@ -423,7 +440,7 @@
     <t>world_standard_population_by_sex</t>
   </si>
   <si>
-    <t xml:space="preserve">World “standard population” by sex</t>
+    <t>World “standard population” by sex</t>
   </si>
   <si>
     <t>OGL</t>
@@ -435,22 +452,22 @@
     <t>likert</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional likert data for demonstration purposes</t>
+    <t>Fictional likert data for demonstration purposes</t>
   </si>
   <si>
     <t>survey_data</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional data for a mortality survey</t>
+    <t>Fictional data for a mortality survey</t>
   </si>
   <si>
     <t>survey_dict</t>
   </si>
   <si>
-    <t xml:space="preserve">Fictional data dictionary for a mortality survey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fictional population data for a mortality survey</t>
+    <t>Fictional data dictionary for a mortality survey</t>
+  </si>
+  <si>
+    <t>Fictional population data for a mortality survey</t>
   </si>
   <si>
     <t>campylobacter_germany</t>
@@ -459,7 +476,7 @@
     <t>campylobacter</t>
   </si>
   <si>
-    <t xml:space="preserve">Campylobacter surveillance data from Germany</t>
+    <t>Campylobacter surveillance data from Germany</t>
   </si>
   <si>
     <t>germany_weather</t>
@@ -468,7 +485,7 @@
     <t>weather</t>
   </si>
   <si>
-    <t xml:space="preserve">Weather data for Germany from 2001-2011</t>
+    <t>Weather data for Germany from 2001-2011</t>
   </si>
   <si>
     <t>multidisease_tests</t>
@@ -477,7 +494,7 @@
     <t>multidisease</t>
   </si>
   <si>
-    <t xml:space="preserve">Test results for notifiable diseases reported in Feveria in 2024</t>
+    <t>Test results for notifiable diseases reported in Feveria in 2024</t>
   </si>
   <si>
     <t>multidisease_surveillance</t>
@@ -486,7 +503,7 @@
     <t>multidisease_notifications</t>
   </si>
   <si>
-    <t xml:space="preserve">Notifiable disease surveillance data in Feveria in 2024</t>
+    <t>Notifiable disease surveillance data in Feveria in 2024</t>
   </si>
   <si>
     <t>multi_maladies_notifications</t>
@@ -519,34 +536,34 @@
     <t>cholera</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 25 May 2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qmd, intror</t>
+    <t>Clean cholera surveillance data for Viraland, 25 May 2021</t>
+  </si>
+  <si>
+    <t>qmd, intror</t>
   </si>
   <si>
     <t>viraland_cholera_20210617_linelist</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 17 June 2021</t>
+    <t>Clean cholera surveillance data for Viraland, 17 June 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist</t>
   </si>
   <si>
-    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 21 July 2021</t>
+    <t>Clean cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist_raw</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw cholera surveillance data for Viraland, 21 July 2021</t>
+    <t>Raw cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_labs</t>
   </si>
   <si>
-    <t xml:space="preserve">Raw cholera lab data for Viraland, 21 July 2021</t>
+    <t>Raw cholera lab data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>feveriosis_main</t>
@@ -555,43 +572,53 @@
     <t>feveriosis</t>
   </si>
   <si>
-    <t xml:space="preserve">Fake endemic vector-borne disease in Feveria 2025-26</t>
-  </si>
-  <si>
     <t>feveriosis_surveillance</t>
   </si>
   <si>
     <t>feveriosis_recent</t>
   </si>
   <si>
-    <t xml:space="preserve">Fake endemic vector-borne disease in Feveria 2025-27</t>
+    <t>Fake endemic vector-borne disease in Viraland 2025-26</t>
+  </si>
+  <si>
+    <t>Fake endemic vector-borne disease in Viraland 2025-27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.500000"/>
+      <sz val="11.5"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -604,31 +631,62 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="2"/>
+          <bgColor indexed="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -641,291 +699,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -1128,29 +903,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="44.33203125"/>
-    <col customWidth="1" min="2" max="2" width="10.33203125"/>
+    <col min="1" max="1" width="44.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="3" width="9"/>
-    <col bestFit="1" customWidth="1" min="4" max="5" width="12.1640625"/>
-    <col bestFit="1" min="8" max="8" width="10.6640625"/>
-    <col bestFit="1" min="9" max="9" width="22.5"/>
-    <col customWidth="1" min="10" max="11" width="11.1640625"/>
-    <col customWidth="1" min="12" max="12" width="5.6640625"/>
-    <col bestFit="1" min="13" max="13" width="10.5"/>
-    <col bestFit="1" min="14" max="14" width="18.1640625"/>
-    <col bestFit="1" min="15" max="15" width="14.33203125"/>
-    <col bestFit="1" min="16" max="16" width="39.6640625"/>
-    <col bestFit="1" min="17" max="17" width="67.5"/>
+    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1"/>
+    <col min="9" max="9" width="22.5" bestFit="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1"/>
+    <col min="14" max="14" width="18.1640625" bestFit="1"/>
+    <col min="15" max="15" width="14.33203125" bestFit="1"/>
+    <col min="16" max="16" width="39.6640625" bestFit="1"/>
+    <col min="17" max="17" width="67.5" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1">
+    <row r="1" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,7 +980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1258,7 +1035,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1313,7 +1090,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_population_1_1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1368,7 +1145,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_1_1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1423,7 +1200,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_2_1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1478,7 +1255,7 @@
         <v>mortality_survey_zzz_2021_survey_1_1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1533,7 +1310,7 @@
         <v>mortality_survey_zzz_2021_dictionary_1_1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1588,7 +1365,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1643,7 +1420,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1698,7 +1475,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1753,7 +1530,7 @@
         <v>covid-19_outbreak_usa_2020_population_1_1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1808,7 +1585,7 @@
         <v>mpox_outbreak_eue_2022_linelist_1_1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1863,7 +1640,7 @@
         <v>mpox_outbreak_eue_2022_aggregate_1_1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1918,7 +1695,7 @@
         <v>salmonella_outbreak_deu_1998_linelist_1_1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1973,7 +1750,7 @@
         <v>influenza_outbreak_chn_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -2028,7 +1805,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -2083,7 +1860,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_2</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -2138,7 +1915,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_3</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -2193,7 +1970,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_4</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -2248,7 +2025,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -2303,7 +2080,7 @@
         <v>ebola_outbreak_sle_2014_dictionary_1_1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -2358,7 +2135,7 @@
         <v>ebola_outbreak_sle_2014_shape_1_1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -2413,7 +2190,7 @@
         <v>ebola_outbreak_sle_2020_population_1_1</v>
       </c>
     </row>
-    <row r="24" ht="15.75">
+    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -2468,7 +2245,7 @@
         <v>ebola_outbreak_sle_2014_other_1_1</v>
       </c>
     </row>
-    <row r="25" ht="15.75">
+    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>103</v>
       </c>
@@ -2523,7 +2300,7 @@
         <v>ebola_outbreak_sle_2014_other_2_1</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -2578,7 +2355,7 @@
         <v>ebola_outbreak_sle_2014_other_3_1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -2633,7 +2410,7 @@
         <v>ebola_outbreak_sle_2014_other_4_1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -2688,7 +2465,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -2743,7 +2520,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_2_1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -2798,7 +2575,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_3_1</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -2853,7 +2630,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_4_1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -2908,7 +2685,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -2963,7 +2740,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_2</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -3018,7 +2795,7 @@
         <v>shigella_surveillance_bel_2013_sequencing_1_1</v>
       </c>
     </row>
-    <row r="35" ht="15.5" customHeight="1">
+    <row r="35" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -3073,7 +2850,7 @@
         <v>shigella_surveillance_bel_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>127</v>
       </c>
@@ -3128,7 +2905,7 @@
         <v>shigella_surveillance_bel_2013_sequencing_1_2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -3183,7 +2960,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -3238,7 +3015,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_2_1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>132</v>
       </c>
@@ -3293,7 +3070,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_3_1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>133</v>
       </c>
@@ -3348,7 +3125,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_4_1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -3403,7 +3180,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_5_1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3458,7 +3235,7 @@
         <v>likert_other_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -3513,7 +3290,7 @@
         <v>mortality_survey_zzz_2021_survey_2_1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -3568,7 +3345,7 @@
         <v>mortality_survey_zzz_2021_dictionary_2_1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -3623,7 +3400,7 @@
         <v>mortality_survey_zzz_2021_population_1_1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -3678,7 +3455,7 @@
         <v>campylobacter_surveillance_deu_2001_linelist_1_1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -3733,7 +3510,7 @@
         <v>weather_other_deu_2001_aggregate_1_1</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -3788,7 +3565,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -3843,7 +3620,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -3898,7 +3675,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -3953,7 +3730,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -4008,7 +3785,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -4063,7 +3840,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -4118,7 +3895,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -4173,7 +3950,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -4228,7 +4005,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_3</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -4283,7 +4060,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_4</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -4338,7 +4115,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_1</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -4393,7 +4170,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_2</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -4448,14 +4225,14 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>177</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" t="s">
         <v>18</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" t="s">
         <v>19</v>
       </c>
       <c r="D61">
@@ -4464,32 +4241,32 @@
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" s="4" t="s">
+      <c r="F61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" t="s">
         <v>40</v>
       </c>
       <c r="H61" t="s">
         <v>76</v>
       </c>
-      <c r="I61" s="4" t="s">
+      <c r="I61" t="s">
         <v>178</v>
       </c>
-      <c r="J61" s="4" t="s">
+      <c r="J61" t="s">
         <v>123</v>
       </c>
-      <c r="K61" s="4" t="s">
+      <c r="K61" t="s">
         <v>42</v>
       </c>
       <c r="L61">
         <v>2025</v>
       </c>
       <c r="M61" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="N61" t="s">
         <v>179</v>
-      </c>
-      <c r="N61" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="O61" t="s">
         <v>28</v>
@@ -4503,14 +4280,14 @@
         <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>181</v>
-      </c>
-      <c r="B62" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" t="s">
         <v>18</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" t="s">
         <v>68</v>
       </c>
       <c r="D62">
@@ -4519,22 +4296,22 @@
       <c r="E62">
         <v>1</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G62" s="4" t="s">
+      <c r="F62" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" t="s">
         <v>40</v>
       </c>
       <c r="H62" t="s">
         <v>76</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" t="s">
         <v>178</v>
       </c>
-      <c r="J62" s="4" t="s">
+      <c r="J62" t="s">
         <v>123</v>
       </c>
-      <c r="K62" s="4" t="s">
+      <c r="K62" t="s">
         <v>42</v>
       </c>
       <c r="L62">
@@ -4543,10 +4320,10 @@
       <c r="M62" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="N62" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="O62" s="4" t="s">
+      <c r="N62" t="s">
+        <v>179</v>
+      </c>
+      <c r="O62" t="s">
         <v>28</v>
       </c>
       <c r="P62" t="str">
@@ -4559,61 +4336,18 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="3" id="{00F30094-00B0-4006-B3DA-002100A30031}">
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A1:A53 A56:A1048576</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="4" id="{006000EA-00CE-4DA1-8999-009E004800A6}">
-            <x14:dxf>
-              <font>
-                <color rgb="FF9C0006"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFFFC7CE"/>
-                  <bgColor rgb="FFFFC7CE"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>A25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{008E009D-00EE-46A3-984F-00500093008B}">
-            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="2"/>
-                  <bgColor indexed="2"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G2:G300 K56:K62</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <conditionalFormatting sqref="A1:A53 A56:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G300 K56:K62">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -1,39 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alanahjansen/Documents/GitHub/appliedepidata/inst/extdata/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15CCCFF-45D0-AF4B-A094-AE47A658DD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="500" windowWidth="20960" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>name</t>
   </si>
@@ -104,7 +87,7 @@
     <t>subnational</t>
   </si>
   <si>
-    <t>acute jaundice syndrome</t>
+    <t xml:space="preserve">acute jaundice syndrome</t>
   </si>
   <si>
     <t>outbreak</t>
@@ -113,13 +96,13 @@
     <t>no</t>
   </si>
   <si>
-    <t>Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
+    <t xml:space="preserve">Linelist data from a real outbreak of Hepatitis E virus (HEV) infection which occurred in the town of Am Timan, Chad, between October 2016 and April 2017.</t>
   </si>
   <si>
     <t>sitrep_walkthroughs</t>
   </si>
   <si>
-    <t>CC by-NC-SA 4.0</t>
+    <t xml:space="preserve">CC by-NC-SA 4.0</t>
   </si>
   <si>
     <t>AJS_AmTiman_population</t>
@@ -128,7 +111,7 @@
     <t>population</t>
   </si>
   <si>
-    <t>Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t xml:space="preserve">Population data from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Blocksshape</t>
@@ -140,13 +123,13 @@
     <t>zip</t>
   </si>
   <si>
-    <t>Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t xml:space="preserve">Shapefile of housing blocks from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>Quartiersshape</t>
   </si>
   <si>
-    <t>Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
+    <t xml:space="preserve">Shapefile of neighbourhoods (fr: quartiers) from an outbreak of Acute Jaundice Syndrome (AJS) in Chad 2016</t>
   </si>
   <si>
     <t>mortality_survey_data</t>
@@ -164,7 +147,7 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Fake data for a mortality survey</t>
+    <t xml:space="preserve">Fake data for a mortality survey</t>
   </si>
   <si>
     <t>gpl3</t>
@@ -176,7 +159,7 @@
     <t>dictionary</t>
   </si>
   <si>
-    <t>Fake data dictionary for a mortality survey</t>
+    <t xml:space="preserve">Fake data dictionary for a mortality survey</t>
   </si>
   <si>
     <t>franglais_AJS_AmTiman</t>
@@ -185,7 +168,7 @@
     <t>fr</t>
   </si>
   <si>
-    <t>quelque chose en francais - oui oui</t>
+    <t xml:space="preserve">quelque chose en francais - oui oui</t>
   </si>
   <si>
     <t>fulton_data</t>
@@ -197,7 +180,7 @@
     <t>covid-19</t>
   </si>
   <si>
-    <t>Jittered COVID-19 linelist data from Fulton County</t>
+    <t xml:space="preserve">Jittered COVID-19 linelist data from Fulton County</t>
   </si>
   <si>
     <t>case_studies</t>
@@ -227,7 +210,7 @@
     <t>mpox</t>
   </si>
   <si>
-    <t>Fictional mpox case linelist in five European countries</t>
+    <t xml:space="preserve">Fictional mpox case linelist in five European countries</t>
   </si>
   <si>
     <t>r_practical</t>
@@ -242,7 +225,7 @@
     <t>csv</t>
   </si>
   <si>
-    <t>Fictional cumulative mpox case counts in five European countries</t>
+    <t xml:space="preserve">Fictional cumulative mpox case counts in five European countries</t>
   </si>
   <si>
     <t>stegentira_data</t>
@@ -254,7 +237,7 @@
     <t>salmonella</t>
   </si>
   <si>
-    <t>Fictional linelist of salmonella outbreak in Stegen, Germany</t>
+    <t xml:space="preserve">Fictional linelist of salmonella outbreak in Stegen, Germany</t>
   </si>
   <si>
     <t>fluH7N9_China_2013</t>
@@ -269,7 +252,7 @@
     <t>influenza</t>
   </si>
   <si>
-    <t>Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
+    <t xml:space="preserve">Linelist data from an outbreak of influenza A H7N9 in China 2013.</t>
   </si>
   <si>
     <t>epirhandbook</t>
@@ -287,52 +270,52 @@
     <t>ebola</t>
   </si>
   <si>
-    <t>Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_excel</t>
   </si>
   <si>
-    <t>Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_rds</t>
   </si>
   <si>
-    <t>R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">R-dataset clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>hospital_linelists</t>
   </si>
   <si>
-    <t>Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Subset of excel clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>linelist_cleaned_with_adm3</t>
   </si>
   <si>
-    <t>Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Subset with additional spatial data of rds clean version of fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>cleaning_dict</t>
   </si>
   <si>
-    <t>Short example cleaning dictionary for the raw linelist</t>
+    <t xml:space="preserve">Short example cleaning dictionary for the raw linelist</t>
   </si>
   <si>
     <t>sle_adm3</t>
   </si>
   <si>
-    <t>Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
-  </si>
-  <si>
-    <t>CC by-IGO</t>
+    <t xml:space="preserve">Shapefile at admin level  3 for Sierra Leone from Humanitarian Data Exchange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC by-IGO</t>
   </si>
   <si>
     <t>sle_admpop_adm3_2020</t>
   </si>
   <si>
-    <t>Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
+    <t xml:space="preserve">Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange</t>
   </si>
   <si>
     <t>epinow_res</t>
@@ -341,7 +324,7 @@
     <t>other</t>
   </si>
   <si>
-    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
+    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014</t>
   </si>
   <si>
     <t>epinow_res_small</t>
@@ -350,7 +333,7 @@
     <t>generation_time</t>
   </si>
   <si>
-    <t>Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
+    <t xml:space="preserve">Outputs from {epinow2} based on fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2015</t>
   </si>
   <si>
     <t>incubation_period</t>
@@ -359,10 +342,10 @@
     <t>cases_clean</t>
   </si>
   <si>
-    <t>contact tracing</t>
-  </si>
-  <si>
-    <t>Fictional case data for a generic disease to demonstrate contact tracing</t>
+    <t xml:space="preserve">contact tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictional case data for a generic disease to demonstrate contact tracing</t>
   </si>
   <si>
     <t>contacts_clean</t>
@@ -383,7 +366,7 @@
     <t>malaria</t>
   </si>
   <si>
-    <t>Fictional counts of malaria cases from Mozambique</t>
+    <t xml:space="preserve">Fictional counts of malaria cases from Mozambique</t>
   </si>
   <si>
     <t>malaria_facility_count_data</t>
@@ -407,25 +390,25 @@
     <t>surveillance</t>
   </si>
   <si>
-    <t>Next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t xml:space="preserve">Next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>sample_data_Shigella_tree</t>
   </si>
   <si>
-    <t>Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
+    <t xml:space="preserve">Linelist data to accompany next generation sequencing data of Shigella surveillance samples from Belgium 2013-2019</t>
   </si>
   <si>
     <t>Shigella_subtree_2</t>
   </si>
   <si>
-    <t>Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
+    <t xml:space="preserve">Analysis output from next generation sequencing data of Shigella surveillance samples from Belgium</t>
   </si>
   <si>
     <t>country_demographics</t>
   </si>
   <si>
-    <t>Fictional country demographic and mortality data to demonstrate standardisation</t>
+    <t xml:space="preserve">Fictional country demographic and mortality data to demonstrate standardisation</t>
   </si>
   <si>
     <t>country_demographics_2</t>
@@ -440,7 +423,7 @@
     <t>world_standard_population_by_sex</t>
   </si>
   <si>
-    <t>World “standard population” by sex</t>
+    <t xml:space="preserve">World “standard population” by sex</t>
   </si>
   <si>
     <t>OGL</t>
@@ -452,22 +435,22 @@
     <t>likert</t>
   </si>
   <si>
-    <t>Fictional likert data for demonstration purposes</t>
+    <t xml:space="preserve">Fictional likert data for demonstration purposes</t>
   </si>
   <si>
     <t>survey_data</t>
   </si>
   <si>
-    <t>Fictional data for a mortality survey</t>
+    <t xml:space="preserve">Fictional data for a mortality survey</t>
   </si>
   <si>
     <t>survey_dict</t>
   </si>
   <si>
-    <t>Fictional data dictionary for a mortality survey</t>
-  </si>
-  <si>
-    <t>Fictional population data for a mortality survey</t>
+    <t xml:space="preserve">Fictional data dictionary for a mortality survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fictional population data for a mortality survey</t>
   </si>
   <si>
     <t>campylobacter_germany</t>
@@ -476,7 +459,7 @@
     <t>campylobacter</t>
   </si>
   <si>
-    <t>Campylobacter surveillance data from Germany</t>
+    <t xml:space="preserve">Campylobacter surveillance data from Germany</t>
   </si>
   <si>
     <t>germany_weather</t>
@@ -485,7 +468,7 @@
     <t>weather</t>
   </si>
   <si>
-    <t>Weather data for Germany from 2001-2011</t>
+    <t xml:space="preserve">Weather data for Germany from 2001-2011</t>
   </si>
   <si>
     <t>multidisease_tests</t>
@@ -494,7 +477,7 @@
     <t>multidisease</t>
   </si>
   <si>
-    <t>Test results for notifiable diseases reported in Feveria in 2024</t>
+    <t xml:space="preserve">Test results for notifiable diseases reported in Feveria in 2024</t>
   </si>
   <si>
     <t>multidisease_surveillance</t>
@@ -503,7 +486,7 @@
     <t>multidisease_notifications</t>
   </si>
   <si>
-    <t>Notifiable disease surveillance data in Feveria in 2024</t>
+    <t xml:space="preserve">Notifiable disease surveillance data in Feveria in 2024</t>
   </si>
   <si>
     <t>multi_maladies_notifications</t>
@@ -536,34 +519,34 @@
     <t>cholera</t>
   </si>
   <si>
-    <t>Clean cholera surveillance data for Viraland, 25 May 2021</t>
-  </si>
-  <si>
-    <t>qmd, intror</t>
+    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 25 May 2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qmd, intror</t>
   </si>
   <si>
     <t>viraland_cholera_20210617_linelist</t>
   </si>
   <si>
-    <t>Clean cholera surveillance data for Viraland, 17 June 2021</t>
+    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 17 June 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist</t>
   </si>
   <si>
-    <t>Clean cholera surveillance data for Viraland, 21 July 2021</t>
+    <t xml:space="preserve">Clean cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_linelist_raw</t>
   </si>
   <si>
-    <t>Raw cholera surveillance data for Viraland, 21 July 2021</t>
+    <t xml:space="preserve">Raw cholera surveillance data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>viraland_cholera_20210721_labs</t>
   </si>
   <si>
-    <t>Raw cholera lab data for Viraland, 21 July 2021</t>
+    <t xml:space="preserve">Raw cholera lab data for Viraland, 21 July 2021</t>
   </si>
   <si>
     <t>feveriosis_main</t>
@@ -572,53 +555,61 @@
     <t>feveriosis</t>
   </si>
   <si>
+    <t xml:space="preserve">Fake endemic vector-borne disease main data in Viraland 2025-26</t>
+  </si>
+  <si>
     <t>feveriosis_surveillance</t>
   </si>
   <si>
     <t>feveriosis_recent</t>
   </si>
   <si>
-    <t>Fake endemic vector-borne disease in Viraland 2025-26</t>
-  </si>
-  <si>
-    <t>Fake endemic vector-borne disease in Viraland 2025-27</t>
+    <t xml:space="preserve">Fake endemic vector-borne disease weekly data in Viraland Sept 2026</t>
+  </si>
+  <si>
+    <t>feveriosis_main_es</t>
+  </si>
+  <si>
+    <t>feveriosis_recent_es</t>
+  </si>
+  <si>
+    <t>feveriosis_main_fr</t>
+  </si>
+  <si>
+    <t>feveriosis_recent_fr</t>
+  </si>
+  <si>
+    <t>feveriosis_main_pt</t>
+  </si>
+  <si>
+    <t>feveriosis_recent_pt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.5"/>
+      <sz val="11.500000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -631,62 +622,37 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="2"/>
-          <bgColor indexed="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -699,8 +665,291 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -903,31 +1152,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="44.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="44.33203125"/>
+    <col customWidth="1" min="2" max="2" width="10.33203125"/>
     <col min="3" max="3" width="9"/>
-    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" bestFit="1"/>
-    <col min="9" max="9" width="22.5" bestFit="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" customWidth="1"/>
-    <col min="13" max="13" width="10.5" bestFit="1"/>
-    <col min="14" max="14" width="18.1640625" bestFit="1"/>
-    <col min="15" max="15" width="14.33203125" bestFit="1"/>
-    <col min="16" max="16" width="39.6640625" bestFit="1"/>
-    <col min="17" max="17" width="67.5" bestFit="1"/>
+    <col bestFit="1" customWidth="1" min="4" max="5" width="12.1640625"/>
+    <col bestFit="1" min="8" max="8" width="10.6640625"/>
+    <col bestFit="1" min="9" max="9" width="22.5"/>
+    <col customWidth="1" min="10" max="10" width="15.140625"/>
+    <col customWidth="1" min="11" max="11" width="11.1640625"/>
+    <col customWidth="1" min="12" max="12" width="11.140625"/>
+    <col customWidth="1" min="13" max="13" width="57.28125"/>
+    <col customWidth="1" min="14" max="14" width="29.421875"/>
+    <col customWidth="1" min="15" max="15" width="24.7109375"/>
+    <col bestFit="1" min="16" max="16" width="39.6640625"/>
+    <col bestFit="1" min="17" max="17" width="67.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -980,7 +1228,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1035,7 +1283,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1090,7 +1338,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_population_1_1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1145,7 +1393,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_1_1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1200,7 +1448,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_shape_2_1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1255,7 +1503,7 @@
         <v>mortality_survey_zzz_2021_survey_1_1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1310,7 +1558,7 @@
         <v>mortality_survey_zzz_2021_dictionary_1_1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1365,7 +1613,7 @@
         <v>acutejaundicesyndrome_outbreak_tcd_2016_linelist_1_1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1420,7 +1668,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1475,7 +1723,7 @@
         <v>covid-19_outbreak_usa_2020_linelist_1_2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1530,7 +1778,7 @@
         <v>covid-19_outbreak_usa_2020_population_1_1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1585,7 +1833,7 @@
         <v>mpox_outbreak_eue_2022_linelist_1_1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1640,7 +1888,7 @@
         <v>mpox_outbreak_eue_2022_aggregate_1_1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1695,7 +1943,7 @@
         <v>salmonella_outbreak_deu_1998_linelist_1_1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1750,7 +1998,7 @@
         <v>influenza_outbreak_chn_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16" t="s">
         <v>81</v>
       </c>
@@ -1805,7 +2053,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -1860,7 +2108,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -1915,7 +2163,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -1970,7 +2218,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -2025,7 +2273,7 @@
         <v>ebola_outbreak_sle_2014_linelist_1_5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -2080,7 +2328,7 @@
         <v>ebola_outbreak_sle_2014_dictionary_1_1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22" t="s">
         <v>95</v>
       </c>
@@ -2135,7 +2383,7 @@
         <v>ebola_outbreak_sle_2014_shape_1_1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -2190,7 +2438,7 @@
         <v>ebola_outbreak_sle_2020_population_1_1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" ht="15.75">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -2245,7 +2493,7 @@
         <v>ebola_outbreak_sle_2014_other_1_1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" ht="15.75">
       <c r="A25" s="2" t="s">
         <v>103</v>
       </c>
@@ -2300,7 +2548,7 @@
         <v>ebola_outbreak_sle_2014_other_2_1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -2355,7 +2603,7 @@
         <v>ebola_outbreak_sle_2014_other_3_1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27" t="s">
         <v>106</v>
       </c>
@@ -2410,7 +2658,7 @@
         <v>ebola_outbreak_sle_2014_other_4_1</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28" t="s">
         <v>107</v>
       </c>
@@ -2465,7 +2713,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_1_1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -2520,7 +2768,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_2_1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -2575,7 +2823,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_3_1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -2630,7 +2878,7 @@
         <v>contacttracing_outbreak_zzz_2020_linelist_4_1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -2685,7 +2933,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -2740,7 +2988,7 @@
         <v>malaria_outbreak_moz_2019_aggregate_1_2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -2795,7 +3043,7 @@
         <v>shigella_surveillance_bel_2013_sequencing_1_1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="15.5" customHeight="1">
       <c r="A35" t="s">
         <v>125</v>
       </c>
@@ -2850,7 +3098,7 @@
         <v>shigella_surveillance_bel_2013_linelist_1_1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36">
       <c r="A36" t="s">
         <v>127</v>
       </c>
@@ -2905,7 +3153,7 @@
         <v>shigella_surveillance_bel_2013_sequencing_1_2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37">
       <c r="A37" t="s">
         <v>129</v>
       </c>
@@ -2960,7 +3208,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38">
       <c r="A38" t="s">
         <v>131</v>
       </c>
@@ -3015,7 +3263,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_2_1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39">
       <c r="A39" t="s">
         <v>132</v>
       </c>
@@ -3070,7 +3318,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_3_1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40">
       <c r="A40" t="s">
         <v>133</v>
       </c>
@@ -3125,7 +3373,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_4_1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -3180,7 +3428,7 @@
         <v>mortality_surveillance_zzz_2020_aggregate_5_1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42">
       <c r="A42" t="s">
         <v>137</v>
       </c>
@@ -3235,7 +3483,7 @@
         <v>likert_other_zzz_2020_aggregate_1_1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -3290,7 +3538,7 @@
         <v>mortality_survey_zzz_2021_survey_2_1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44">
       <c r="A44" t="s">
         <v>142</v>
       </c>
@@ -3345,7 +3593,7 @@
         <v>mortality_survey_zzz_2021_dictionary_2_1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45">
       <c r="A45" t="s">
         <v>30</v>
       </c>
@@ -3400,7 +3648,7 @@
         <v>mortality_survey_zzz_2021_population_1_1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -3455,7 +3703,7 @@
         <v>campylobacter_surveillance_deu_2001_linelist_1_1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -3510,7 +3758,7 @@
         <v>weather_other_deu_2001_aggregate_1_1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -3565,7 +3813,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49" t="s">
         <v>155</v>
       </c>
@@ -3620,7 +3868,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -3675,7 +3923,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -3730,7 +3978,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -3785,7 +4033,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -3840,7 +4088,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="54">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -3895,7 +4143,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_2_1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -3950,7 +4198,7 @@
         <v>multidisease_surveillance_zzz_2024_linelist_1_1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -4005,7 +4253,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57">
       <c r="A57" t="s">
         <v>169</v>
       </c>
@@ -4060,7 +4308,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_4</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -4115,7 +4363,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="59">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -4170,7 +4418,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_2</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -4225,7 +4473,7 @@
         <v>cholera_surveillance_zzz_2021_linelist_1_5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="61">
       <c r="A61" t="s">
         <v>177</v>
       </c>
@@ -4263,10 +4511,10 @@
         <v>2025</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O61" t="s">
         <v>28</v>
@@ -4280,9 +4528,9 @@
         <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62">
       <c r="A62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B62" t="s">
         <v>18</v>
@@ -4321,7 +4569,7 @@
         <v>182</v>
       </c>
       <c r="N62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O62" t="s">
         <v>28</v>
@@ -4335,19 +4583,440 @@
         <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
       </c>
     </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="6">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>160</v>
+      </c>
+      <c r="G63" t="s">
+        <v>40</v>
+      </c>
+      <c r="H63" t="s">
+        <v>76</v>
+      </c>
+      <c r="I63" t="s">
+        <v>178</v>
+      </c>
+      <c r="J63" t="s">
+        <v>123</v>
+      </c>
+      <c r="K63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63">
+        <v>2025</v>
+      </c>
+      <c r="M63" t="s">
+        <v>179</v>
+      </c>
+      <c r="N63" t="s">
+        <v>180</v>
+      </c>
+      <c r="O63" t="s">
+        <v>28</v>
+      </c>
+      <c r="P63" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I63," ",""),"_",J63,"_",G63,"_",L63)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q63" t="str">
+        <f>CONCATENATE(P63,"_",B63,"_",D63,"_",E63)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+      </c>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="6">
+        <v>2</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" t="s">
+        <v>40</v>
+      </c>
+      <c r="H64" t="s">
+        <v>76</v>
+      </c>
+      <c r="I64" t="s">
+        <v>178</v>
+      </c>
+      <c r="J64" t="s">
+        <v>123</v>
+      </c>
+      <c r="K64" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64">
+        <v>2025</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N64" t="s">
+        <v>180</v>
+      </c>
+      <c r="O64" t="s">
+        <v>28</v>
+      </c>
+      <c r="P64" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I64," ",""),"_",J64,"_",G64,"_",L64)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q64" t="str">
+        <f>CONCATENATE(P64,"_",B64,"_",D64,"_",E64)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="6">
+        <v>1</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>49</v>
+      </c>
+      <c r="G65" t="s">
+        <v>40</v>
+      </c>
+      <c r="H65" t="s">
+        <v>76</v>
+      </c>
+      <c r="I65" t="s">
+        <v>178</v>
+      </c>
+      <c r="J65" t="s">
+        <v>123</v>
+      </c>
+      <c r="K65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65">
+        <v>2025</v>
+      </c>
+      <c r="M65" t="s">
+        <v>179</v>
+      </c>
+      <c r="N65" t="s">
+        <v>180</v>
+      </c>
+      <c r="O65" t="s">
+        <v>28</v>
+      </c>
+      <c r="P65" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I65," ",""),"_",J65,"_",G65,"_",L65)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q65" t="str">
+        <f>CONCATENATE(P65,"_",B65,"_",D65,"_",E65)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" s="6">
+        <v>2</v>
+      </c>
+      <c r="E66" s="6">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>49</v>
+      </c>
+      <c r="G66" t="s">
+        <v>40</v>
+      </c>
+      <c r="H66" t="s">
+        <v>76</v>
+      </c>
+      <c r="I66" t="s">
+        <v>178</v>
+      </c>
+      <c r="J66" t="s">
+        <v>123</v>
+      </c>
+      <c r="K66" t="s">
+        <v>42</v>
+      </c>
+      <c r="L66">
+        <v>2025</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N66" t="s">
+        <v>180</v>
+      </c>
+      <c r="O66" t="s">
+        <v>28</v>
+      </c>
+      <c r="P66" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I66," ",""),"_",J66,"_",G66,"_",L66)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q66" t="str">
+        <f>CONCATENATE(P66,"_",B66,"_",D66,"_",E66)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="6">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>163</v>
+      </c>
+      <c r="G67" t="s">
+        <v>40</v>
+      </c>
+      <c r="H67" t="s">
+        <v>76</v>
+      </c>
+      <c r="I67" t="s">
+        <v>178</v>
+      </c>
+      <c r="J67" t="s">
+        <v>123</v>
+      </c>
+      <c r="K67" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67">
+        <v>2025</v>
+      </c>
+      <c r="M67" t="s">
+        <v>179</v>
+      </c>
+      <c r="N67" t="s">
+        <v>180</v>
+      </c>
+      <c r="O67" t="s">
+        <v>28</v>
+      </c>
+      <c r="P67" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I67," ",""),"_",J67,"_",G67,"_",L67)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q67" t="str">
+        <f>CONCATENATE(P67,"_",B67,"_",D67,"_",E67)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="6">
+        <v>2</v>
+      </c>
+      <c r="E68" s="6">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>163</v>
+      </c>
+      <c r="G68" t="s">
+        <v>40</v>
+      </c>
+      <c r="H68" t="s">
+        <v>76</v>
+      </c>
+      <c r="I68" t="s">
+        <v>178</v>
+      </c>
+      <c r="J68" t="s">
+        <v>123</v>
+      </c>
+      <c r="K68" t="s">
+        <v>42</v>
+      </c>
+      <c r="L68">
+        <v>2025</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N68" t="s">
+        <v>180</v>
+      </c>
+      <c r="O68" t="s">
+        <v>28</v>
+      </c>
+      <c r="P68" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I68," ",""),"_",J68,"_",G68,"_",L68)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q68" t="str">
+        <f>CONCATENATE(P68,"_",B68,"_",D68,"_",E68)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A53 A56:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G300 K56:K62">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{00C500EE-0089-4CF4-A8CF-00DE00C40055}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A1:A53 A56:A1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="4" id="{00840057-0091-4DB8-B1CC-001100B000DD}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A25</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{0068003F-0096-44AA-B755-00E2007A0031}">
+            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="2"/>
+                  <bgColor indexed="2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G2:G62 G69:G300 K56:K62 G63 K63 G64 K64 G65 K65 G66 K66 G67 K67 G68 K68</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{00C70060-0083-4DA4-B2F7-00F70013002C}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A63:A64</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{00EA0076-009B-4467-98F3-00B90083004C}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A65:A66</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{009000C2-00F3-4716-9CBB-00D900660031}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A67:A68</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t>name</t>
   </si>
@@ -583,6 +583,15 @@
   </si>
   <si>
     <t>feveriosis_recent_pt</t>
+  </si>
+  <si>
+    <t>feveriosis_main_ru</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>feveriosis_recent_ru</t>
   </si>
 </sst>
 </file>
@@ -4590,13 +4599,13 @@
       <c r="B63" t="s">
         <v>18</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="6">
-        <v>1</v>
-      </c>
-      <c r="E63" s="6">
+      <c r="D63" s="5">
+        <v>1</v>
+      </c>
+      <c r="E63" s="5">
         <v>1</v>
       </c>
       <c r="F63" t="s">
@@ -4630,11 +4639,11 @@
         <v>28</v>
       </c>
       <c r="P63" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I63," ",""),"_",J63,"_",G63,"_",L63)</f>
+        <f t="shared" ref="P63:P68" si="2">CONCATENATE(SUBSTITUTE(I63," ",""),"_",J63,"_",G63,"_",L63)</f>
         <v>feveriosis_surveillance_zzz_2025</v>
       </c>
       <c r="Q63" t="str">
-        <f>CONCATENATE(P63,"_",B63,"_",D63,"_",E63)</f>
+        <f t="shared" ref="Q63:Q68" si="3">CONCATENATE(P63,"_",B63,"_",D63,"_",E63)</f>
         <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
       </c>
     </row>
@@ -4645,13 +4654,13 @@
       <c r="B64" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="5">
         <v>2</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64" s="5">
         <v>1</v>
       </c>
       <c r="F64" t="s">
@@ -4685,11 +4694,11 @@
         <v>28</v>
       </c>
       <c r="P64" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I64," ",""),"_",J64,"_",G64,"_",L64)</f>
+        <f t="shared" si="2"/>
         <v>feveriosis_surveillance_zzz_2025</v>
       </c>
       <c r="Q64" t="str">
-        <f>CONCATENATE(P64,"_",B64,"_",D64,"_",E64)</f>
+        <f t="shared" si="3"/>
         <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
       </c>
     </row>
@@ -4700,13 +4709,13 @@
       <c r="B65" t="s">
         <v>18</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="6">
-        <v>1</v>
-      </c>
-      <c r="E65" s="6">
+      <c r="D65" s="5">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5">
         <v>1</v>
       </c>
       <c r="F65" t="s">
@@ -4740,11 +4749,11 @@
         <v>28</v>
       </c>
       <c r="P65" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I65," ",""),"_",J65,"_",G65,"_",L65)</f>
+        <f t="shared" si="2"/>
         <v>feveriosis_surveillance_zzz_2025</v>
       </c>
       <c r="Q65" t="str">
-        <f>CONCATENATE(P65,"_",B65,"_",D65,"_",E65)</f>
+        <f t="shared" si="3"/>
         <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
       </c>
     </row>
@@ -4755,13 +4764,13 @@
       <c r="B66" t="s">
         <v>18</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="5">
         <v>2</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="5">
         <v>1</v>
       </c>
       <c r="F66" t="s">
@@ -4795,11 +4804,11 @@
         <v>28</v>
       </c>
       <c r="P66" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I66," ",""),"_",J66,"_",G66,"_",L66)</f>
+        <f t="shared" si="2"/>
         <v>feveriosis_surveillance_zzz_2025</v>
       </c>
       <c r="Q66" t="str">
-        <f>CONCATENATE(P66,"_",B66,"_",D66,"_",E66)</f>
+        <f t="shared" si="3"/>
         <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
       </c>
     </row>
@@ -4810,13 +4819,13 @@
       <c r="B67" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="6">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6">
+      <c r="D67" s="5">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5">
         <v>1</v>
       </c>
       <c r="F67" t="s">
@@ -4850,11 +4859,11 @@
         <v>28</v>
       </c>
       <c r="P67" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I67," ",""),"_",J67,"_",G67,"_",L67)</f>
+        <f t="shared" si="2"/>
         <v>feveriosis_surveillance_zzz_2025</v>
       </c>
       <c r="Q67" t="str">
-        <f>CONCATENATE(P67,"_",B67,"_",D67,"_",E67)</f>
+        <f t="shared" si="3"/>
         <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
       </c>
     </row>
@@ -4865,13 +4874,13 @@
       <c r="B68" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="5">
         <v>2</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="5">
         <v>1</v>
       </c>
       <c r="F68" t="s">
@@ -4905,11 +4914,121 @@
         <v>28</v>
       </c>
       <c r="P68" t="str">
-        <f>CONCATENATE(SUBSTITUTE(I68," ",""),"_",J68,"_",G68,"_",L68)</f>
+        <f t="shared" si="2"/>
         <v>feveriosis_surveillance_zzz_2025</v>
       </c>
       <c r="Q68" t="str">
-        <f>CONCATENATE(P68,"_",B68,"_",D68,"_",E68)</f>
+        <f t="shared" si="3"/>
+        <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69" s="5">
+        <v>2025</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="N69" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P69" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I69," ",""),"_",J69,"_",G69,"_",L69)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q69" t="str">
+        <f>CONCATENATE(P69,"_",B69,"_",D69,"_",E69)</f>
+        <v>feveriosis_surveillance_zzz_2025_linelist_1_1</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" s="5">
+        <v>2</v>
+      </c>
+      <c r="E70" s="5">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L70" s="5">
+        <v>2025</v>
+      </c>
+      <c r="M70" t="s">
+        <v>182</v>
+      </c>
+      <c r="N70" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="O70" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P70" t="str">
+        <f>CONCATENATE(SUBSTITUTE(I70," ",""),"_",J70,"_",G70,"_",L70)</f>
+        <v>feveriosis_surveillance_zzz_2025</v>
+      </c>
+      <c r="Q70" t="str">
+        <f>CONCATENATE(P70,"_",B70,"_",D70,"_",E70)</f>
         <v>feveriosis_surveillance_zzz_2025_linelist_2_1</v>
       </c>
     </row>
@@ -4922,7 +5041,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="3" id="{00C500EE-0089-4CF4-A8CF-00DE00C40055}">
+          <x14:cfRule type="duplicateValues" priority="3" id="{006A00A0-00EE-4BB6-8FF8-008D008F0062}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -4938,7 +5057,7 @@
           <xm:sqref>A1:A53 A56:A1048576</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="4" id="{00840057-0091-4DB8-B1CC-001100B000DD}">
+          <x14:cfRule type="duplicateValues" priority="4" id="{00B100C2-0033-4359-ABE7-005B00DC0097}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -4954,7 +5073,7 @@
           <xm:sqref>A25</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{0068003F-0096-44AA-B755-00E2007A0031}">
+          <x14:cfRule type="expression" priority="1" id="{00740091-0030-488C-97B7-004B00FB003E}">
             <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
             <x14:dxf>
               <fill>
@@ -4968,7 +5087,7 @@
           <xm:sqref>G2:G62 G69:G300 K56:K62 G63 K63 G64 K64 G65 K65 G66 K66 G67 K67 G68 K68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="3" id="{00C70060-0083-4DA4-B2F7-00F70013002C}">
+          <x14:cfRule type="duplicateValues" priority="3" id="{00DA0081-00E8-43CB-B215-004C00C400E2}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -4984,7 +5103,7 @@
           <xm:sqref>A63:A64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="3" id="{00EA0076-009B-4467-98F3-00B90083004C}">
+          <x14:cfRule type="duplicateValues" priority="3" id="{005A00E9-0014-4E5B-AEBE-00F600880094}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -5000,7 +5119,7 @@
           <xm:sqref>A65:A66</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="duplicateValues" priority="3" id="{009000C2-00F3-4716-9CBB-00D900660031}">
+          <x14:cfRule type="duplicateValues" priority="3" id="{00430085-00A1-40C2-B707-000100860069}">
             <x14:dxf>
               <font>
                 <color rgb="FF9C0006"/>
@@ -5015,6 +5134,80 @@
           </x14:cfRule>
           <xm:sqref>A67:A68</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{003500F5-002D-4149-9A57-00CC007600F9}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A69:A70</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00A5003B-008E-4281-8EA7-00D8000200E2}">
+            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="2"/>
+                  <bgColor indexed="2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G69 G70</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="duplicateValues" priority="3" id="{005D0041-004B-41BB-8106-004A00480043}">
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A69:A70</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{00F90051-0021-458E-B61C-006C005A0042}">
+            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="2"/>
+                  <bgColor indexed="2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{006B009B-007F-4C55-BA9B-002C00BD0087}">
+            <xm:f>AND(LEN(G2)&lt;&gt;3,LEN(G2)&lt;&gt;0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="2"/>
+                  <bgColor indexed="2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K70</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisfernandoquezada/Documents/GitHub/appliedepidata/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2164287B-C64B-EF49-9B73-E6289DF431EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4F97E1-17D5-1747-8E8E-1FDC2B07A506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="317">
   <si>
     <t>name</t>
   </si>
@@ -863,6 +863,114 @@
   </si>
   <si>
     <t>case_linelists_outbreak_sle_2014_dictionary_1_1</t>
+  </si>
+  <si>
+    <t>example_case_linelist_2020_10_08</t>
+  </si>
+  <si>
+    <t>example_case_linelist</t>
+  </si>
+  <si>
+    <t>Dated snapshot (2020-10-08) of fictional case linelist data for the West African Ebola outbreak of 2014, for an iteration/loops example folder (same content as linelist_raw)</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_1</t>
+  </si>
+  <si>
+    <t>example_hospital_linelists</t>
+  </si>
+  <si>
+    <t>Combined all-hospital cleaned linelist for the West African Ebola outbreak of 2014, for an iteration/loops example folder (same content as hospital_linelists)</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_2</t>
+  </si>
+  <si>
+    <t>example_central_hospital</t>
+  </si>
+  <si>
+    <t>Central Hospital subset of the cleaned Ebola linelist, one of six per-hospital files for an iteration/loops example</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_3</t>
+  </si>
+  <si>
+    <t>example_military_hospital</t>
+  </si>
+  <si>
+    <t>Military Hospital subset of the cleaned Ebola linelist, one of six per-hospital files for an iteration/loops example</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_4</t>
+  </si>
+  <si>
+    <t>example_port_hospital</t>
+  </si>
+  <si>
+    <t>Port Hospital subset of the cleaned Ebola linelist, one of six per-hospital files for an iteration/loops example</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_5</t>
+  </si>
+  <si>
+    <t>example_st_marks_maternity_hospital</t>
+  </si>
+  <si>
+    <t>St. Mark's Maternity Hospital (SMMH) subset of the cleaned Ebola linelist, one of six per-hospital files for an iteration/loops example</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_6</t>
+  </si>
+  <si>
+    <t>example_missing</t>
+  </si>
+  <si>
+    <t>Missing-hospital subset of the cleaned Ebola linelist, one of six per-hospital files for an iteration/loops example</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_7</t>
+  </si>
+  <si>
+    <t>example_other</t>
+  </si>
+  <si>
+    <t>Other-hospital subset of the cleaned Ebola linelist, one of six per-hospital files for an iteration/loops example</t>
+  </si>
+  <si>
+    <t>example_case_linelist_outbreak_sle_2014_linelist_1_8</t>
+  </si>
+  <si>
+    <t>example_fluH7N9_China_2013</t>
+  </si>
+  <si>
+    <t>example_influenza</t>
+  </si>
+  <si>
+    <t>Linelist data from an outbreak of influenza A H7N9 in China 2013, for an iteration/loops example folder (same content as fluH7N9_China_2013)</t>
+  </si>
+  <si>
+    <t>example_influenza_outbreak_chn_2013</t>
+  </si>
+  <si>
+    <t>example_influenza_outbreak_chn_2013_linelist_1_1</t>
+  </si>
+  <si>
+    <t>example_district_weekly_count_data</t>
+  </si>
+  <si>
+    <t>example_malaria</t>
+  </si>
+  <si>
+    <t>Fictional counts of malaria cases from Mozambique, for an iteration/loops example folder (same content as district_weekly_count_data)</t>
+  </si>
+  <si>
+    <t>example_malaria_outbreak_moz_2019</t>
+  </si>
+  <si>
+    <t>example_malaria_outbreak_moz_2019_aggregate_1_1</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
@@ -1229,7 +1337,7 @@
     <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="123" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="132.1640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="35.83203125" bestFit="1" customWidth="1"/>
@@ -5209,6 +5317,536 @@
       </c>
       <c r="Q75" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" t="s">
+        <v>101</v>
+      </c>
+      <c r="H76" t="s">
+        <v>93</v>
+      </c>
+      <c r="I76" t="s">
+        <v>282</v>
+      </c>
+      <c r="J76" t="s">
+        <v>24</v>
+      </c>
+      <c r="K76" t="s">
+        <v>47</v>
+      </c>
+      <c r="L76">
+        <v>2014</v>
+      </c>
+      <c r="M76" t="s">
+        <v>283</v>
+      </c>
+      <c r="N76" t="s">
+        <v>96</v>
+      </c>
+      <c r="O76" t="s">
+        <v>97</v>
+      </c>
+      <c r="P76" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>286</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" t="s">
+        <v>101</v>
+      </c>
+      <c r="H77" t="s">
+        <v>93</v>
+      </c>
+      <c r="I77" t="s">
+        <v>282</v>
+      </c>
+      <c r="J77" t="s">
+        <v>24</v>
+      </c>
+      <c r="K77" t="s">
+        <v>47</v>
+      </c>
+      <c r="L77">
+        <v>2014</v>
+      </c>
+      <c r="M77" t="s">
+        <v>287</v>
+      </c>
+      <c r="N77" t="s">
+        <v>96</v>
+      </c>
+      <c r="O77" t="s">
+        <v>97</v>
+      </c>
+      <c r="P77" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>289</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>82</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+      <c r="F78" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" t="s">
+        <v>101</v>
+      </c>
+      <c r="H78" t="s">
+        <v>93</v>
+      </c>
+      <c r="I78" t="s">
+        <v>282</v>
+      </c>
+      <c r="J78" t="s">
+        <v>24</v>
+      </c>
+      <c r="K78" t="s">
+        <v>47</v>
+      </c>
+      <c r="L78">
+        <v>2014</v>
+      </c>
+      <c r="M78" t="s">
+        <v>290</v>
+      </c>
+      <c r="N78" t="s">
+        <v>96</v>
+      </c>
+      <c r="O78" t="s">
+        <v>97</v>
+      </c>
+      <c r="P78" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>292</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="F79" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>101</v>
+      </c>
+      <c r="H79" t="s">
+        <v>93</v>
+      </c>
+      <c r="I79" t="s">
+        <v>282</v>
+      </c>
+      <c r="J79" t="s">
+        <v>24</v>
+      </c>
+      <c r="K79" t="s">
+        <v>47</v>
+      </c>
+      <c r="L79">
+        <v>2014</v>
+      </c>
+      <c r="M79" t="s">
+        <v>293</v>
+      </c>
+      <c r="N79" t="s">
+        <v>96</v>
+      </c>
+      <c r="O79" t="s">
+        <v>97</v>
+      </c>
+      <c r="P79" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>295</v>
+      </c>
+      <c r="B80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>5</v>
+      </c>
+      <c r="F80" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>101</v>
+      </c>
+      <c r="H80" t="s">
+        <v>93</v>
+      </c>
+      <c r="I80" t="s">
+        <v>282</v>
+      </c>
+      <c r="J80" t="s">
+        <v>24</v>
+      </c>
+      <c r="K80" t="s">
+        <v>47</v>
+      </c>
+      <c r="L80">
+        <v>2014</v>
+      </c>
+      <c r="M80" t="s">
+        <v>296</v>
+      </c>
+      <c r="N80" t="s">
+        <v>96</v>
+      </c>
+      <c r="O80" t="s">
+        <v>97</v>
+      </c>
+      <c r="P80" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>298</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>6</v>
+      </c>
+      <c r="F81" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" t="s">
+        <v>101</v>
+      </c>
+      <c r="H81" t="s">
+        <v>93</v>
+      </c>
+      <c r="I81" t="s">
+        <v>282</v>
+      </c>
+      <c r="J81" t="s">
+        <v>24</v>
+      </c>
+      <c r="K81" t="s">
+        <v>47</v>
+      </c>
+      <c r="L81">
+        <v>2014</v>
+      </c>
+      <c r="M81" t="s">
+        <v>299</v>
+      </c>
+      <c r="N81" t="s">
+        <v>96</v>
+      </c>
+      <c r="O81" t="s">
+        <v>97</v>
+      </c>
+      <c r="P81" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>7</v>
+      </c>
+      <c r="F82" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" t="s">
+        <v>101</v>
+      </c>
+      <c r="H82" t="s">
+        <v>93</v>
+      </c>
+      <c r="I82" t="s">
+        <v>282</v>
+      </c>
+      <c r="J82" t="s">
+        <v>24</v>
+      </c>
+      <c r="K82" t="s">
+        <v>47</v>
+      </c>
+      <c r="L82">
+        <v>2014</v>
+      </c>
+      <c r="M82" t="s">
+        <v>302</v>
+      </c>
+      <c r="N82" t="s">
+        <v>96</v>
+      </c>
+      <c r="O82" t="s">
+        <v>97</v>
+      </c>
+      <c r="P82" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>304</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>8</v>
+      </c>
+      <c r="F83" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" t="s">
+        <v>101</v>
+      </c>
+      <c r="H83" t="s">
+        <v>93</v>
+      </c>
+      <c r="I83" t="s">
+        <v>282</v>
+      </c>
+      <c r="J83" t="s">
+        <v>24</v>
+      </c>
+      <c r="K83" t="s">
+        <v>47</v>
+      </c>
+      <c r="L83">
+        <v>2014</v>
+      </c>
+      <c r="M83" t="s">
+        <v>305</v>
+      </c>
+      <c r="N83" t="s">
+        <v>96</v>
+      </c>
+      <c r="O83" t="s">
+        <v>97</v>
+      </c>
+      <c r="P83" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>307</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" t="s">
+        <v>92</v>
+      </c>
+      <c r="H84" t="s">
+        <v>93</v>
+      </c>
+      <c r="I84" t="s">
+        <v>308</v>
+      </c>
+      <c r="J84" t="s">
+        <v>24</v>
+      </c>
+      <c r="K84" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84">
+        <v>2013</v>
+      </c>
+      <c r="M84" t="s">
+        <v>309</v>
+      </c>
+      <c r="N84" t="s">
+        <v>96</v>
+      </c>
+      <c r="O84" t="s">
+        <v>97</v>
+      </c>
+      <c r="P84" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>312</v>
+      </c>
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" t="s">
+        <v>152</v>
+      </c>
+      <c r="H85" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" t="s">
+        <v>313</v>
+      </c>
+      <c r="J85" t="s">
+        <v>24</v>
+      </c>
+      <c r="K85" t="s">
+        <v>47</v>
+      </c>
+      <c r="L85">
+        <v>2019</v>
+      </c>
+      <c r="M85" t="s">
+        <v>314</v>
+      </c>
+      <c r="N85" t="s">
+        <v>96</v>
+      </c>
+      <c r="O85" t="s">
+        <v>28</v>
+      </c>
+      <c r="P85" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisfernandoquezada/Documents/GitHub/appliedepidata/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4F97E1-17D5-1747-8E8E-1FDC2B07A506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A20780-7B04-CB40-B1B7-5BD8D4A0A739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="333">
   <si>
     <t>name</t>
   </si>
@@ -971,6 +971,54 @@
   </si>
   <si>
     <t>example_malaria_outbreak_moz_2019_aggregate_1_1</t>
+  </si>
+  <si>
+    <t>gis_population_sle_admpop_adm3_2020</t>
+  </si>
+  <si>
+    <t>gis_basics</t>
+  </si>
+  <si>
+    <t>mapping</t>
+  </si>
+  <si>
+    <t>Population data at admin level 3 for Sierra Leone from Humanitarian Data Exchange, repackaged for the GIS basics mapping example (same content as sle_admpop_adm3_2020)</t>
+  </si>
+  <si>
+    <t>gis_basics_sle_2020</t>
+  </si>
+  <si>
+    <t>gis_basics_sle_2020_population_1_1</t>
+  </si>
+  <si>
+    <t>gis_linelist_cleaned_with_adm3</t>
+  </si>
+  <si>
+    <t>Cleaned fictional Ebola Virus Disease linelist joined with admin-3 spatial data, repackaged for the GIS basics mapping example (same content as linelist_cleaned_with_adm3)</t>
+  </si>
+  <si>
+    <t>gis_basics_sle_2020_linelist_1_2</t>
+  </si>
+  <si>
+    <t>gis_covid_incidence</t>
+  </si>
+  <si>
+    <t>global</t>
+  </si>
+  <si>
+    <t>Fictional cumulative COVID-19 incidence by country, created for the GIS basics choropleth mapping example</t>
+  </si>
+  <si>
+    <t>gis_basics_sle_2020_aggregate_1_3</t>
+  </si>
+  <si>
+    <t>gis_population_sle_population_statistics_sierraleone_2020</t>
+  </si>
+  <si>
+    <t>Age/sex population proportions for Sierra Leone from Humanitarian Data Exchange, for the GIS basics population pyramid example</t>
+  </si>
+  <si>
+    <t>gis_basics_sle_2020_population_1_4</t>
   </si>
 </sst>
 </file>
@@ -1323,10 +1371,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
@@ -1337,7 +1385,7 @@
     <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="132.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="136.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="35.83203125" bestFit="1" customWidth="1"/>
@@ -5847,6 +5895,218 @@
       </c>
       <c r="Q85" t="s">
         <v>316</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>317</v>
+      </c>
+      <c r="B86" t="s">
+        <v>32</v>
+      </c>
+      <c r="C86" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" t="s">
+        <v>101</v>
+      </c>
+      <c r="H86" t="s">
+        <v>93</v>
+      </c>
+      <c r="I86" t="s">
+        <v>318</v>
+      </c>
+      <c r="J86" t="s">
+        <v>319</v>
+      </c>
+      <c r="K86" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86">
+        <v>2020</v>
+      </c>
+      <c r="M86" t="s">
+        <v>320</v>
+      </c>
+      <c r="N86" t="s">
+        <v>96</v>
+      </c>
+      <c r="O86" t="s">
+        <v>123</v>
+      </c>
+      <c r="P86" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>323</v>
+      </c>
+      <c r="B87" t="s">
+        <v>18</v>
+      </c>
+      <c r="C87" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" t="s">
+        <v>101</v>
+      </c>
+      <c r="H87" t="s">
+        <v>93</v>
+      </c>
+      <c r="I87" t="s">
+        <v>318</v>
+      </c>
+      <c r="J87" t="s">
+        <v>319</v>
+      </c>
+      <c r="K87" t="s">
+        <v>47</v>
+      </c>
+      <c r="L87">
+        <v>2014</v>
+      </c>
+      <c r="M87" t="s">
+        <v>324</v>
+      </c>
+      <c r="N87" t="s">
+        <v>96</v>
+      </c>
+      <c r="O87" t="s">
+        <v>97</v>
+      </c>
+      <c r="P87" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>326</v>
+      </c>
+      <c r="B88" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" t="s">
+        <v>327</v>
+      </c>
+      <c r="H88" t="s">
+        <v>327</v>
+      </c>
+      <c r="I88" t="s">
+        <v>318</v>
+      </c>
+      <c r="J88" t="s">
+        <v>319</v>
+      </c>
+      <c r="K88" t="s">
+        <v>47</v>
+      </c>
+      <c r="L88">
+        <v>2020</v>
+      </c>
+      <c r="M88" t="s">
+        <v>328</v>
+      </c>
+      <c r="N88" t="s">
+        <v>96</v>
+      </c>
+      <c r="O88" t="s">
+        <v>28</v>
+      </c>
+      <c r="P88" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>330</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>4</v>
+      </c>
+      <c r="F89" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" t="s">
+        <v>101</v>
+      </c>
+      <c r="H89" t="s">
+        <v>93</v>
+      </c>
+      <c r="I89" t="s">
+        <v>318</v>
+      </c>
+      <c r="J89" t="s">
+        <v>319</v>
+      </c>
+      <c r="K89" t="s">
+        <v>25</v>
+      </c>
+      <c r="L89">
+        <v>2020</v>
+      </c>
+      <c r="M89" t="s">
+        <v>331</v>
+      </c>
+      <c r="N89" t="s">
+        <v>96</v>
+      </c>
+      <c r="O89" t="s">
+        <v>123</v>
+      </c>
+      <c r="P89" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisfernandoquezada/Documents/GitHub/appliedepidata/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A20780-7B04-CB40-B1B7-5BD8D4A0A739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4957B8AB-0A16-6548-909B-EE5D4A200723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="378">
   <si>
     <t>name</t>
   </si>
@@ -1019,6 +1019,141 @@
   </si>
   <si>
     <t>gis_basics_sle_2020_population_1_4</t>
+  </si>
+  <si>
+    <t>gis_africa_countries</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>afr</t>
+  </si>
+  <si>
+    <t>international</t>
+  </si>
+  <si>
+    <t>Natural Earth Admin-0 country boundaries filtered to the African continent, for the GIS basics mapping example</t>
+  </si>
+  <si>
+    <t>Public Domain</t>
+  </si>
+  <si>
+    <t>gis_basics_afr_2020</t>
+  </si>
+  <si>
+    <t>gis_basics_afr_2020_shape_1_1</t>
+  </si>
+  <si>
+    <t>linelist_cleaned</t>
+  </si>
+  <si>
+    <t>Cleaned fictional Ebola Virus Disease data simulating properties from the West African Ebola outbreak of 2014, added under a plain name (same content as linelist_cleaned_excel)</t>
+  </si>
+  <si>
+    <t>ebola_outbreak_sle_2014_linelist_1_6</t>
+  </si>
+  <si>
+    <t>epidemic_models_epinow_res</t>
+  </si>
+  <si>
+    <t>Outputs from {epinow2}, for the epidemic models example (same content as epinow_res)</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_1_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_epinow_res_small</t>
+  </si>
+  <si>
+    <t>Outputs from {epinow2} (small), for the epidemic models example (same content as epinow_res_small)</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_2_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_generation_time</t>
+  </si>
+  <si>
+    <t>Generation time distribution, for the epidemic models example (same content as generation_time)</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_3_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_incubation_period</t>
+  </si>
+  <si>
+    <t>Incubation period distribution, for the epidemic models example (same content as incubation_period)</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_4_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_estimate_samples</t>
+  </si>
+  <si>
+    <t>Posterior estimate samples unbundled from epinow_res$estimates$samples, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_5_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_estimated_reported_cases_samples</t>
+  </si>
+  <si>
+    <t>Posterior estimated-reported-cases samples unbundled from epinow_res$estimated_reported_cases$samples, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_6_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_latest_date</t>
+  </si>
+  <si>
+    <t>Latest observation date unbundled from epinow_res$estimates$observations, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_7_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_reported_cases</t>
+  </si>
+  <si>
+    <t>Reported case counts unbundled from epinow_res$estimates$observations, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_8_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_summarised_estimated_reported_cases</t>
+  </si>
+  <si>
+    <t>Summarised estimated reported cases unbundled from epinow_res$estimated_reported_cases$summarised, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_9_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_summarised_estimates</t>
+  </si>
+  <si>
+    <t>Summarised estimates unbundled from epinow_res$estimates$summarised, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_10_1</t>
+  </si>
+  <si>
+    <t>epidemic_models_summary</t>
+  </si>
+  <si>
+    <t>Model run summary unbundled from epinow_res$summary, for the epidemic models example</t>
+  </si>
+  <si>
+    <t>epidemic_models_sle_2014_other_11_1</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" bestFit="1" customWidth="1"/>
@@ -1380,12 +1515,12 @@
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="136.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="137.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="35.83203125" bestFit="1" customWidth="1"/>
@@ -6107,6 +6242,695 @@
       </c>
       <c r="Q89" t="s">
         <v>332</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>333</v>
+      </c>
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" t="s">
+        <v>334</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" t="s">
+        <v>335</v>
+      </c>
+      <c r="H90" t="s">
+        <v>336</v>
+      </c>
+      <c r="I90" t="s">
+        <v>318</v>
+      </c>
+      <c r="J90" t="s">
+        <v>319</v>
+      </c>
+      <c r="K90" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90">
+        <v>2020</v>
+      </c>
+      <c r="M90" t="s">
+        <v>337</v>
+      </c>
+      <c r="N90" t="s">
+        <v>96</v>
+      </c>
+      <c r="O90" t="s">
+        <v>338</v>
+      </c>
+      <c r="P90" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>341</v>
+      </c>
+      <c r="B91" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>6</v>
+      </c>
+      <c r="F91" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" t="s">
+        <v>101</v>
+      </c>
+      <c r="H91" t="s">
+        <v>93</v>
+      </c>
+      <c r="I91" t="s">
+        <v>102</v>
+      </c>
+      <c r="J91" t="s">
+        <v>24</v>
+      </c>
+      <c r="K91" t="s">
+        <v>47</v>
+      </c>
+      <c r="L91">
+        <v>2014</v>
+      </c>
+      <c r="M91" t="s">
+        <v>342</v>
+      </c>
+      <c r="N91" t="s">
+        <v>96</v>
+      </c>
+      <c r="O91" t="s">
+        <v>97</v>
+      </c>
+      <c r="P91" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>344</v>
+      </c>
+      <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" t="s">
+        <v>67</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" t="s">
+        <v>101</v>
+      </c>
+      <c r="H92" t="s">
+        <v>93</v>
+      </c>
+      <c r="I92" t="s">
+        <v>102</v>
+      </c>
+      <c r="J92" t="s">
+        <v>24</v>
+      </c>
+      <c r="K92" t="s">
+        <v>47</v>
+      </c>
+      <c r="L92">
+        <v>2014</v>
+      </c>
+      <c r="M92" t="s">
+        <v>345</v>
+      </c>
+      <c r="N92" t="s">
+        <v>96</v>
+      </c>
+      <c r="O92" t="s">
+        <v>97</v>
+      </c>
+      <c r="P92" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>348</v>
+      </c>
+      <c r="B93" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" t="s">
+        <v>67</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" t="s">
+        <v>101</v>
+      </c>
+      <c r="H93" t="s">
+        <v>93</v>
+      </c>
+      <c r="I93" t="s">
+        <v>102</v>
+      </c>
+      <c r="J93" t="s">
+        <v>24</v>
+      </c>
+      <c r="K93" t="s">
+        <v>47</v>
+      </c>
+      <c r="L93">
+        <v>2014</v>
+      </c>
+      <c r="M93" t="s">
+        <v>349</v>
+      </c>
+      <c r="N93" t="s">
+        <v>96</v>
+      </c>
+      <c r="O93" t="s">
+        <v>97</v>
+      </c>
+      <c r="P93" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>351</v>
+      </c>
+      <c r="B94" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94">
+        <v>3</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" t="s">
+        <v>101</v>
+      </c>
+      <c r="H94" t="s">
+        <v>93</v>
+      </c>
+      <c r="I94" t="s">
+        <v>102</v>
+      </c>
+      <c r="J94" t="s">
+        <v>24</v>
+      </c>
+      <c r="K94" t="s">
+        <v>47</v>
+      </c>
+      <c r="L94">
+        <v>2014</v>
+      </c>
+      <c r="M94" t="s">
+        <v>352</v>
+      </c>
+      <c r="N94" t="s">
+        <v>96</v>
+      </c>
+      <c r="O94" t="s">
+        <v>97</v>
+      </c>
+      <c r="P94" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>354</v>
+      </c>
+      <c r="B95" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" t="s">
+        <v>67</v>
+      </c>
+      <c r="D95">
+        <v>4</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" t="s">
+        <v>101</v>
+      </c>
+      <c r="H95" t="s">
+        <v>93</v>
+      </c>
+      <c r="I95" t="s">
+        <v>102</v>
+      </c>
+      <c r="J95" t="s">
+        <v>24</v>
+      </c>
+      <c r="K95" t="s">
+        <v>47</v>
+      </c>
+      <c r="L95">
+        <v>2014</v>
+      </c>
+      <c r="M95" t="s">
+        <v>355</v>
+      </c>
+      <c r="N95" t="s">
+        <v>96</v>
+      </c>
+      <c r="O95" t="s">
+        <v>97</v>
+      </c>
+      <c r="P95" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>357</v>
+      </c>
+      <c r="B96" t="s">
+        <v>130</v>
+      </c>
+      <c r="C96" t="s">
+        <v>67</v>
+      </c>
+      <c r="D96">
+        <v>5</v>
+      </c>
+      <c r="E96">
+        <v>1</v>
+      </c>
+      <c r="F96" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" t="s">
+        <v>101</v>
+      </c>
+      <c r="H96" t="s">
+        <v>93</v>
+      </c>
+      <c r="I96" t="s">
+        <v>102</v>
+      </c>
+      <c r="J96" t="s">
+        <v>24</v>
+      </c>
+      <c r="K96" t="s">
+        <v>47</v>
+      </c>
+      <c r="L96">
+        <v>2014</v>
+      </c>
+      <c r="M96" t="s">
+        <v>358</v>
+      </c>
+      <c r="N96" t="s">
+        <v>96</v>
+      </c>
+      <c r="O96" t="s">
+        <v>97</v>
+      </c>
+      <c r="P96" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>360</v>
+      </c>
+      <c r="B97" t="s">
+        <v>130</v>
+      </c>
+      <c r="C97" t="s">
+        <v>67</v>
+      </c>
+      <c r="D97">
+        <v>6</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" t="s">
+        <v>101</v>
+      </c>
+      <c r="H97" t="s">
+        <v>93</v>
+      </c>
+      <c r="I97" t="s">
+        <v>102</v>
+      </c>
+      <c r="J97" t="s">
+        <v>24</v>
+      </c>
+      <c r="K97" t="s">
+        <v>47</v>
+      </c>
+      <c r="L97">
+        <v>2014</v>
+      </c>
+      <c r="M97" t="s">
+        <v>361</v>
+      </c>
+      <c r="N97" t="s">
+        <v>96</v>
+      </c>
+      <c r="O97" t="s">
+        <v>97</v>
+      </c>
+      <c r="P97" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>363</v>
+      </c>
+      <c r="B98" t="s">
+        <v>130</v>
+      </c>
+      <c r="C98" t="s">
+        <v>67</v>
+      </c>
+      <c r="D98">
+        <v>7</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>101</v>
+      </c>
+      <c r="H98" t="s">
+        <v>93</v>
+      </c>
+      <c r="I98" t="s">
+        <v>102</v>
+      </c>
+      <c r="J98" t="s">
+        <v>24</v>
+      </c>
+      <c r="K98" t="s">
+        <v>47</v>
+      </c>
+      <c r="L98">
+        <v>2014</v>
+      </c>
+      <c r="M98" t="s">
+        <v>364</v>
+      </c>
+      <c r="N98" t="s">
+        <v>96</v>
+      </c>
+      <c r="O98" t="s">
+        <v>97</v>
+      </c>
+      <c r="P98" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>366</v>
+      </c>
+      <c r="B99" t="s">
+        <v>130</v>
+      </c>
+      <c r="C99" t="s">
+        <v>67</v>
+      </c>
+      <c r="D99">
+        <v>8</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" t="s">
+        <v>101</v>
+      </c>
+      <c r="H99" t="s">
+        <v>93</v>
+      </c>
+      <c r="I99" t="s">
+        <v>102</v>
+      </c>
+      <c r="J99" t="s">
+        <v>24</v>
+      </c>
+      <c r="K99" t="s">
+        <v>47</v>
+      </c>
+      <c r="L99">
+        <v>2014</v>
+      </c>
+      <c r="M99" t="s">
+        <v>367</v>
+      </c>
+      <c r="N99" t="s">
+        <v>96</v>
+      </c>
+      <c r="O99" t="s">
+        <v>97</v>
+      </c>
+      <c r="P99" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>369</v>
+      </c>
+      <c r="B100" t="s">
+        <v>130</v>
+      </c>
+      <c r="C100" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100">
+        <v>9</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>101</v>
+      </c>
+      <c r="H100" t="s">
+        <v>93</v>
+      </c>
+      <c r="I100" t="s">
+        <v>102</v>
+      </c>
+      <c r="J100" t="s">
+        <v>24</v>
+      </c>
+      <c r="K100" t="s">
+        <v>47</v>
+      </c>
+      <c r="L100">
+        <v>2014</v>
+      </c>
+      <c r="M100" t="s">
+        <v>370</v>
+      </c>
+      <c r="N100" t="s">
+        <v>96</v>
+      </c>
+      <c r="O100" t="s">
+        <v>97</v>
+      </c>
+      <c r="P100" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>372</v>
+      </c>
+      <c r="B101" t="s">
+        <v>130</v>
+      </c>
+      <c r="C101" t="s">
+        <v>67</v>
+      </c>
+      <c r="D101">
+        <v>10</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" t="s">
+        <v>101</v>
+      </c>
+      <c r="H101" t="s">
+        <v>93</v>
+      </c>
+      <c r="I101" t="s">
+        <v>102</v>
+      </c>
+      <c r="J101" t="s">
+        <v>24</v>
+      </c>
+      <c r="K101" t="s">
+        <v>47</v>
+      </c>
+      <c r="L101">
+        <v>2014</v>
+      </c>
+      <c r="M101" t="s">
+        <v>373</v>
+      </c>
+      <c r="N101" t="s">
+        <v>96</v>
+      </c>
+      <c r="O101" t="s">
+        <v>97</v>
+      </c>
+      <c r="P101" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>375</v>
+      </c>
+      <c r="B102" t="s">
+        <v>130</v>
+      </c>
+      <c r="C102" t="s">
+        <v>67</v>
+      </c>
+      <c r="D102">
+        <v>11</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" t="s">
+        <v>101</v>
+      </c>
+      <c r="H102" t="s">
+        <v>93</v>
+      </c>
+      <c r="I102" t="s">
+        <v>102</v>
+      </c>
+      <c r="J102" t="s">
+        <v>24</v>
+      </c>
+      <c r="K102" t="s">
+        <v>47</v>
+      </c>
+      <c r="L102">
+        <v>2014</v>
+      </c>
+      <c r="M102" t="s">
+        <v>376</v>
+      </c>
+      <c r="N102" t="s">
+        <v>96</v>
+      </c>
+      <c r="O102" t="s">
+        <v>97</v>
+      </c>
+      <c r="P102" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luisfernandoquezada/Documents/GitHub/appliedepidata/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4957B8AB-0A16-6548-909B-EE5D4A200723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51D0A16-24C9-EC46-8BCB-7230D7040C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="19720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$1</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -6934,6 +6937,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8784,6 +8784,87 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>sle_hf</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>shape</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>sle</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>national</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>outbreak</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L105">
+        <v>2014</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Health facility points for Sierra Leone from OpenStreetMap via the Humanitarian Data Exchange</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>epirhandbook</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>ODbL</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>ebola_outbreak_sle_2014</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>ebola_outbreak_sle_2014_shape_2_1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inst/extdata/tableoftables.xlsx
+++ b/inst/extdata/tableoftables.xlsx
@@ -1,20 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t xml:space="preserve">ebola_outbreak_sle_2014_shape_1_2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -24,12 +32,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,11 +358,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q105"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
@@ -457,10 +465,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,7 +501,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>2016</v>
       </c>
       <c r="M2" t="inlineStr">
@@ -538,10 +546,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -574,7 +582,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>2016</v>
       </c>
       <c r="M3" t="inlineStr">
@@ -619,10 +627,10 @@
           <t>zip</t>
         </is>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -655,7 +663,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>2016</v>
       </c>
       <c r="M4" t="inlineStr">
@@ -700,10 +708,10 @@
           <t>zip</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -736,7 +744,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>2016</v>
       </c>
       <c r="M5" t="inlineStr">
@@ -781,10 +789,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -817,7 +825,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>2021</v>
       </c>
       <c r="M6" t="inlineStr">
@@ -862,10 +870,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -898,7 +906,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>2021</v>
       </c>
       <c r="M7" t="inlineStr">
@@ -943,10 +951,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -979,7 +987,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>2016</v>
       </c>
       <c r="M8" t="inlineStr">
@@ -1024,10 +1032,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -1060,7 +1068,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>2020</v>
       </c>
       <c r="M9" t="inlineStr">
@@ -1105,10 +1113,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -1141,7 +1149,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>2020</v>
       </c>
       <c r="M10" t="inlineStr">
@@ -1186,10 +1194,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -1222,7 +1230,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>2020</v>
       </c>
       <c r="M11" t="inlineStr">
@@ -1267,10 +1275,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -1303,7 +1311,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>2022</v>
       </c>
       <c r="M12" t="inlineStr">
@@ -1348,10 +1356,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -1384,7 +1392,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>2022</v>
       </c>
       <c r="M13" t="inlineStr">
@@ -1429,10 +1437,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -1465,7 +1473,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>1998</v>
       </c>
       <c r="M14" t="inlineStr">
@@ -1510,10 +1518,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -1546,7 +1554,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>2013</v>
       </c>
       <c r="M15" t="inlineStr">
@@ -1591,10 +1599,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -1627,7 +1635,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>2014</v>
       </c>
       <c r="M16" t="inlineStr">
@@ -1672,10 +1680,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -1708,7 +1716,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>2014</v>
       </c>
       <c r="M17" t="inlineStr">
@@ -1753,10 +1761,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1797,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>2014</v>
       </c>
       <c r="M18" t="inlineStr">
@@ -1834,10 +1842,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
         <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -1870,7 +1878,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>2014</v>
       </c>
       <c r="M19" t="inlineStr">
@@ -1915,10 +1923,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -1951,7 +1959,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>2014</v>
       </c>
       <c r="M20" t="inlineStr">
@@ -1996,10 +2004,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -2032,7 +2040,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>2014</v>
       </c>
       <c r="M21" t="inlineStr">
@@ -2077,11 +2085,11 @@
           <t>zip</t>
         </is>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2113,7 +2121,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>2014</v>
       </c>
       <c r="M22" t="inlineStr">
@@ -2136,10 +2144,8 @@
           <t>ebola_outbreak_sle_2014</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>ebola_outbreak_sle_2014_shape_1_1</t>
-        </is>
+      <c r="Q22" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2158,10 +2164,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -2194,7 +2200,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>2020</v>
       </c>
       <c r="M23" t="inlineStr">
@@ -2239,10 +2245,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -2275,7 +2281,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>2014</v>
       </c>
       <c r="M24" t="inlineStr">
@@ -2320,10 +2326,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>2</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -2356,7 +2362,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>2014</v>
       </c>
       <c r="M25" t="inlineStr">
@@ -2401,10 +2407,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -2437,7 +2443,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>2014</v>
       </c>
       <c r="M26" t="inlineStr">
@@ -2482,10 +2488,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>4</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -2518,7 +2524,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>2014</v>
       </c>
       <c r="M27" t="inlineStr">
@@ -2563,10 +2569,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
@@ -2599,7 +2605,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>2020</v>
       </c>
       <c r="M28" t="inlineStr">
@@ -2644,10 +2650,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>2</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -2680,7 +2686,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>2020</v>
       </c>
       <c r="M29" t="inlineStr">
@@ -2725,10 +2731,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>3</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -2761,7 +2767,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>2020</v>
       </c>
       <c r="M30" t="inlineStr">
@@ -2806,10 +2812,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>4</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -2842,7 +2848,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>2020</v>
       </c>
       <c r="M31" t="inlineStr">
@@ -2887,10 +2893,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -2923,7 +2929,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>2019</v>
       </c>
       <c r="M32" t="inlineStr">
@@ -2968,10 +2974,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
         <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -3004,7 +3010,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>2019</v>
       </c>
       <c r="M33" t="inlineStr">
@@ -3049,10 +3055,10 @@
           <t>txt</t>
         </is>
       </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -3085,7 +3091,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>2013</v>
       </c>
       <c r="M34" t="inlineStr">
@@ -3130,10 +3136,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
@@ -3166,7 +3172,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>2013</v>
       </c>
       <c r="M35" t="inlineStr">
@@ -3211,10 +3217,10 @@
           <t>txt</t>
         </is>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>2</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -3247,7 +3253,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>2013</v>
       </c>
       <c r="M36" t="inlineStr">
@@ -3292,10 +3298,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -3328,7 +3334,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>2020</v>
       </c>
       <c r="M37" t="inlineStr">
@@ -3373,10 +3379,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D38">
+      <c r="D38" t="n">
         <v>2</v>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -3409,7 +3415,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L38">
+      <c r="L38" t="n">
         <v>2020</v>
       </c>
       <c r="M38" t="inlineStr">
@@ -3454,10 +3460,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -3490,7 +3496,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L39">
+      <c r="L39" t="n">
         <v>2020</v>
       </c>
       <c r="M39" t="inlineStr">
@@ -3535,10 +3541,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D40">
+      <c r="D40" t="n">
         <v>4</v>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -3571,7 +3577,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L40">
+      <c r="L40" t="n">
         <v>2020</v>
       </c>
       <c r="M40" t="inlineStr">
@@ -3616,10 +3622,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D41">
+      <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -3652,7 +3658,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L41">
+      <c r="L41" t="n">
         <v>2020</v>
       </c>
       <c r="M41" t="inlineStr">
@@ -3697,10 +3703,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42">
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
@@ -3733,7 +3739,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L42">
+      <c r="L42" t="n">
         <v>2020</v>
       </c>
       <c r="M42" t="inlineStr">
@@ -3778,10 +3784,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D43">
+      <c r="D43" t="n">
         <v>2</v>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -3814,7 +3820,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L43">
+      <c r="L43" t="n">
         <v>2021</v>
       </c>
       <c r="M43" t="inlineStr">
@@ -3859,10 +3865,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D44">
+      <c r="D44" t="n">
         <v>2</v>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -3895,7 +3901,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L44">
+      <c r="L44" t="n">
         <v>2021</v>
       </c>
       <c r="M44" t="inlineStr">
@@ -3940,10 +3946,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -3976,7 +3982,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L45">
+      <c r="L45" t="n">
         <v>2021</v>
       </c>
       <c r="M45" t="inlineStr">
@@ -4021,10 +4027,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46">
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -4057,7 +4063,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L46">
+      <c r="L46" t="n">
         <v>2001</v>
       </c>
       <c r="M46" t="inlineStr">
@@ -4102,10 +4108,10 @@
           <t>zip</t>
         </is>
       </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47">
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -4138,7 +4144,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L47">
+      <c r="L47" t="n">
         <v>2001</v>
       </c>
       <c r="M47" t="inlineStr">
@@ -4183,10 +4189,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48">
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -4219,7 +4225,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L48">
+      <c r="L48" t="n">
         <v>2024</v>
       </c>
       <c r="M48" t="inlineStr">
@@ -4264,10 +4270,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D49">
+      <c r="D49" t="n">
         <v>2</v>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
@@ -4300,7 +4306,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L49">
+      <c r="L49" t="n">
         <v>2024</v>
       </c>
       <c r="M49" t="inlineStr">
@@ -4345,10 +4351,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D50">
+      <c r="D50" t="n">
         <v>2</v>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -4381,7 +4387,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L50">
+      <c r="L50" t="n">
         <v>2024</v>
       </c>
       <c r="M50" t="inlineStr">
@@ -4426,10 +4432,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -4462,7 +4468,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L51">
+      <c r="L51" t="n">
         <v>2024</v>
       </c>
       <c r="M51" t="inlineStr">
@@ -4507,10 +4513,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D52">
+      <c r="D52" t="n">
         <v>2</v>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -4543,7 +4549,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L52">
+      <c r="L52" t="n">
         <v>2024</v>
       </c>
       <c r="M52" t="inlineStr">
@@ -4588,10 +4594,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53">
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -4624,7 +4630,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L53">
+      <c r="L53" t="n">
         <v>2024</v>
       </c>
       <c r="M53" t="inlineStr">
@@ -4669,10 +4675,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D54">
+      <c r="D54" t="n">
         <v>2</v>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -4705,7 +4711,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L54">
+      <c r="L54" t="n">
         <v>2024</v>
       </c>
       <c r="M54" t="inlineStr">
@@ -4750,10 +4756,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55">
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -4786,7 +4792,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L55">
+      <c r="L55" t="n">
         <v>2024</v>
       </c>
       <c r="M55" t="inlineStr">
@@ -4831,10 +4837,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56">
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
         <v>3</v>
       </c>
       <c r="F56" t="inlineStr">
@@ -4867,7 +4873,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L56">
+      <c r="L56" t="n">
         <v>2021</v>
       </c>
       <c r="M56" t="inlineStr">
@@ -4912,10 +4918,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57">
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
         <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -4948,7 +4954,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L57">
+      <c r="L57" t="n">
         <v>2021</v>
       </c>
       <c r="M57" t="inlineStr">
@@ -4993,10 +4999,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58">
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
         <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -5029,7 +5035,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L58">
+      <c r="L58" t="n">
         <v>2021</v>
       </c>
       <c r="M58" t="inlineStr">
@@ -5074,10 +5080,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
         <v>2</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -5110,7 +5116,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L59">
+      <c r="L59" t="n">
         <v>2021</v>
       </c>
       <c r="M59" t="inlineStr">
@@ -5155,10 +5161,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
         <v>5</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -5191,7 +5197,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L60">
+      <c r="L60" t="n">
         <v>2021</v>
       </c>
       <c r="M60" t="inlineStr">
@@ -5236,10 +5242,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61">
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -5272,7 +5278,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L61">
+      <c r="L61" t="n">
         <v>2025</v>
       </c>
       <c r="M61" t="inlineStr">
@@ -5317,10 +5323,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D62">
+      <c r="D62" t="n">
         <v>2</v>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>1</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -5353,7 +5359,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L62">
+      <c r="L62" t="n">
         <v>2025</v>
       </c>
       <c r="M62" t="inlineStr">
@@ -5398,10 +5404,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63">
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
         <v>1</v>
       </c>
       <c r="F63" t="inlineStr">
@@ -5434,7 +5440,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L63">
+      <c r="L63" t="n">
         <v>2025</v>
       </c>
       <c r="M63" t="inlineStr">
@@ -5479,10 +5485,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D64">
+      <c r="D64" t="n">
         <v>2</v>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>1</v>
       </c>
       <c r="F64" t="inlineStr">
@@ -5515,7 +5521,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L64">
+      <c r="L64" t="n">
         <v>2025</v>
       </c>
       <c r="M64" t="inlineStr">
@@ -5560,10 +5566,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65">
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
@@ -5596,7 +5602,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L65">
+      <c r="L65" t="n">
         <v>2025</v>
       </c>
       <c r="M65" t="inlineStr">
@@ -5641,10 +5647,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D66">
+      <c r="D66" t="n">
         <v>2</v>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="inlineStr">
@@ -5677,7 +5683,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L66">
+      <c r="L66" t="n">
         <v>2025</v>
       </c>
       <c r="M66" t="inlineStr">
@@ -5722,10 +5728,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67">
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
         <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -5758,7 +5764,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L67">
+      <c r="L67" t="n">
         <v>2025</v>
       </c>
       <c r="M67" t="inlineStr">
@@ -5803,10 +5809,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D68">
+      <c r="D68" t="n">
         <v>2</v>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
@@ -5839,7 +5845,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L68">
+      <c r="L68" t="n">
         <v>2025</v>
       </c>
       <c r="M68" t="inlineStr">
@@ -5884,10 +5890,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
@@ -5920,7 +5926,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L69">
+      <c r="L69" t="n">
         <v>2025</v>
       </c>
       <c r="M69" t="inlineStr">
@@ -5965,10 +5971,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D70">
+      <c r="D70" t="n">
         <v>2</v>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
@@ -6001,7 +6007,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L70">
+      <c r="L70" t="n">
         <v>2025</v>
       </c>
       <c r="M70" t="inlineStr">
@@ -6046,10 +6052,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D71">
+      <c r="D71" t="n">
         <v>2</v>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
@@ -6082,7 +6088,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L71">
+      <c r="L71" t="n">
         <v>2001</v>
       </c>
       <c r="M71" t="inlineStr">
@@ -6127,10 +6133,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72">
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
         <v>1</v>
       </c>
       <c r="F72" t="inlineStr">
@@ -6163,7 +6169,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L72">
+      <c r="L72" t="n">
         <v>2014</v>
       </c>
       <c r="M72" t="inlineStr">
@@ -6208,10 +6214,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73">
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
         <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
@@ -6244,7 +6250,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L73">
+      <c r="L73" t="n">
         <v>2014</v>
       </c>
       <c r="M73" t="inlineStr">
@@ -6289,10 +6295,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74">
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
         <v>3</v>
       </c>
       <c r="F74" t="inlineStr">
@@ -6325,7 +6331,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L74">
+      <c r="L74" t="n">
         <v>2014</v>
       </c>
       <c r="M74" t="inlineStr">
@@ -6370,10 +6376,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
@@ -6406,7 +6412,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L75">
+      <c r="L75" t="n">
         <v>2014</v>
       </c>
       <c r="M75" t="inlineStr">
@@ -6451,10 +6457,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
         <v>1</v>
       </c>
       <c r="F76" t="inlineStr">
@@ -6487,7 +6493,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L76">
+      <c r="L76" t="n">
         <v>2014</v>
       </c>
       <c r="M76" t="inlineStr">
@@ -6532,10 +6538,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
         <v>2</v>
       </c>
       <c r="F77" t="inlineStr">
@@ -6568,7 +6574,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L77">
+      <c r="L77" t="n">
         <v>2014</v>
       </c>
       <c r="M77" t="inlineStr">
@@ -6613,10 +6619,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="E78">
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
         <v>3</v>
       </c>
       <c r="F78" t="inlineStr">
@@ -6649,7 +6655,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L78">
+      <c r="L78" t="n">
         <v>2014</v>
       </c>
       <c r="M78" t="inlineStr">
@@ -6694,10 +6700,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="E79">
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
         <v>4</v>
       </c>
       <c r="F79" t="inlineStr">
@@ -6730,7 +6736,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L79">
+      <c r="L79" t="n">
         <v>2014</v>
       </c>
       <c r="M79" t="inlineStr">
@@ -6775,10 +6781,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80">
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
         <v>5</v>
       </c>
       <c r="F80" t="inlineStr">
@@ -6811,7 +6817,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L80">
+      <c r="L80" t="n">
         <v>2014</v>
       </c>
       <c r="M80" t="inlineStr">
@@ -6856,10 +6862,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81">
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
         <v>6</v>
       </c>
       <c r="F81" t="inlineStr">
@@ -6892,7 +6898,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L81">
+      <c r="L81" t="n">
         <v>2014</v>
       </c>
       <c r="M81" t="inlineStr">
@@ -6937,10 +6943,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D82">
-        <v>1</v>
-      </c>
-      <c r="E82">
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
         <v>7</v>
       </c>
       <c r="F82" t="inlineStr">
@@ -6973,7 +6979,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L82">
+      <c r="L82" t="n">
         <v>2014</v>
       </c>
       <c r="M82" t="inlineStr">
@@ -7018,10 +7024,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83">
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
         <v>8</v>
       </c>
       <c r="F83" t="inlineStr">
@@ -7054,7 +7060,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L83">
+      <c r="L83" t="n">
         <v>2014</v>
       </c>
       <c r="M83" t="inlineStr">
@@ -7099,10 +7105,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84">
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
         <v>1</v>
       </c>
       <c r="F84" t="inlineStr">
@@ -7135,7 +7141,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L84">
+      <c r="L84" t="n">
         <v>2013</v>
       </c>
       <c r="M84" t="inlineStr">
@@ -7180,10 +7186,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-      <c r="E85">
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="inlineStr">
@@ -7216,7 +7222,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L85">
+      <c r="L85" t="n">
         <v>2019</v>
       </c>
       <c r="M85" t="inlineStr">
@@ -7261,10 +7267,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D86">
-        <v>1</v>
-      </c>
-      <c r="E86">
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="inlineStr">
@@ -7297,7 +7303,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L86">
+      <c r="L86" t="n">
         <v>2020</v>
       </c>
       <c r="M86" t="inlineStr">
@@ -7342,10 +7348,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-      <c r="E87">
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
         <v>2</v>
       </c>
       <c r="F87" t="inlineStr">
@@ -7378,7 +7384,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L87">
+      <c r="L87" t="n">
         <v>2014</v>
       </c>
       <c r="M87" t="inlineStr">
@@ -7423,10 +7429,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88">
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
         <v>3</v>
       </c>
       <c r="F88" t="inlineStr">
@@ -7459,7 +7465,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L88">
+      <c r="L88" t="n">
         <v>2020</v>
       </c>
       <c r="M88" t="inlineStr">
@@ -7504,10 +7510,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D89">
-        <v>1</v>
-      </c>
-      <c r="E89">
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
         <v>4</v>
       </c>
       <c r="F89" t="inlineStr">
@@ -7540,7 +7546,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L89">
+      <c r="L89" t="n">
         <v>2020</v>
       </c>
       <c r="M89" t="inlineStr">
@@ -7585,10 +7591,10 @@
           <t>json</t>
         </is>
       </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
         <v>1</v>
       </c>
       <c r="F90" t="inlineStr">
@@ -7621,7 +7627,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L90">
+      <c r="L90" t="n">
         <v>2020</v>
       </c>
       <c r="M90" t="inlineStr">
@@ -7666,10 +7672,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91">
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
         <v>6</v>
       </c>
       <c r="F91" t="inlineStr">
@@ -7702,7 +7708,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L91">
+      <c r="L91" t="n">
         <v>2014</v>
       </c>
       <c r="M91" t="inlineStr">
@@ -7747,10 +7753,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92">
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
         <v>1</v>
       </c>
       <c r="F92" t="inlineStr">
@@ -7783,7 +7789,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L92">
+      <c r="L92" t="n">
         <v>2014</v>
       </c>
       <c r="M92" t="inlineStr">
@@ -7828,10 +7834,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D93">
+      <c r="D93" t="n">
         <v>2</v>
       </c>
-      <c r="E93">
+      <c r="E93" t="n">
         <v>1</v>
       </c>
       <c r="F93" t="inlineStr">
@@ -7864,7 +7870,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L93">
+      <c r="L93" t="n">
         <v>2014</v>
       </c>
       <c r="M93" t="inlineStr">
@@ -7909,10 +7915,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D94">
+      <c r="D94" t="n">
         <v>3</v>
       </c>
-      <c r="E94">
+      <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="inlineStr">
@@ -7945,7 +7951,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L94">
+      <c r="L94" t="n">
         <v>2014</v>
       </c>
       <c r="M94" t="inlineStr">
@@ -7990,10 +7996,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D95">
+      <c r="D95" t="n">
         <v>4</v>
       </c>
-      <c r="E95">
+      <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="inlineStr">
@@ -8026,7 +8032,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L95">
+      <c r="L95" t="n">
         <v>2014</v>
       </c>
       <c r="M95" t="inlineStr">
@@ -8071,10 +8077,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D96">
+      <c r="D96" t="n">
         <v>5</v>
       </c>
-      <c r="E96">
+      <c r="E96" t="n">
         <v>1</v>
       </c>
       <c r="F96" t="inlineStr">
@@ -8107,7 +8113,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L96">
+      <c r="L96" t="n">
         <v>2014</v>
       </c>
       <c r="M96" t="inlineStr">
@@ -8152,10 +8158,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D97">
+      <c r="D97" t="n">
         <v>6</v>
       </c>
-      <c r="E97">
+      <c r="E97" t="n">
         <v>1</v>
       </c>
       <c r="F97" t="inlineStr">
@@ -8188,7 +8194,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L97">
+      <c r="L97" t="n">
         <v>2014</v>
       </c>
       <c r="M97" t="inlineStr">
@@ -8233,10 +8239,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D98">
+      <c r="D98" t="n">
         <v>7</v>
       </c>
-      <c r="E98">
+      <c r="E98" t="n">
         <v>1</v>
       </c>
       <c r="F98" t="inlineStr">
@@ -8269,7 +8275,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L98">
+      <c r="L98" t="n">
         <v>2014</v>
       </c>
       <c r="M98" t="inlineStr">
@@ -8314,10 +8320,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D99">
+      <c r="D99" t="n">
         <v>8</v>
       </c>
-      <c r="E99">
+      <c r="E99" t="n">
         <v>1</v>
       </c>
       <c r="F99" t="inlineStr">
@@ -8350,7 +8356,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L99">
+      <c r="L99" t="n">
         <v>2014</v>
       </c>
       <c r="M99" t="inlineStr">
@@ -8395,10 +8401,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D100">
+      <c r="D100" t="n">
         <v>9</v>
       </c>
-      <c r="E100">
+      <c r="E100" t="n">
         <v>1</v>
       </c>
       <c r="F100" t="inlineStr">
@@ -8431,7 +8437,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L100">
+      <c r="L100" t="n">
         <v>2014</v>
       </c>
       <c r="M100" t="inlineStr">
@@ -8476,10 +8482,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D101">
+      <c r="D101" t="n">
         <v>10</v>
       </c>
-      <c r="E101">
+      <c r="E101" t="n">
         <v>1</v>
       </c>
       <c r="F101" t="inlineStr">
@@ -8512,7 +8518,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L101">
+      <c r="L101" t="n">
         <v>2014</v>
       </c>
       <c r="M101" t="inlineStr">
@@ -8557,10 +8563,10 @@
           <t>rds</t>
         </is>
       </c>
-      <c r="D102">
+      <c r="D102" t="n">
         <v>11</v>
       </c>
-      <c r="E102">
+      <c r="E102" t="n">
         <v>1</v>
       </c>
       <c r="F102" t="inlineStr">
@@ -8593,7 +8599,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L102">
+      <c r="L102" t="n">
         <v>2014</v>
       </c>
       <c r="M102" t="inlineStr">
@@ -8638,10 +8644,10 @@
           <t>csv</t>
         </is>
       </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103">
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
         <v>1</v>
       </c>
       <c r="F103" t="inlineStr">
@@ -8674,7 +8680,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L103">
+      <c r="L103" t="n">
         <v>2024</v>
       </c>
       <c r="M103" t="inlineStr">
@@ -8719,10 +8725,10 @@
           <t>xlsx</t>
         </is>
       </c>
-      <c r="D104">
+      <c r="D104" t="n">
         <v>2</v>
       </c>
-      <c r="E104">
+      <c r="E104" t="n">
         <v>1</v>
       </c>
       <c r="F104" t="inlineStr">
@@ -8755,7 +8761,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L104">
+      <c r="L104" t="n">
         <v>2024</v>
       </c>
       <c r="M104" t="inlineStr">
@@ -8800,10 +8806,10 @@
           <t>zip</t>
         </is>
       </c>
-      <c r="D105">
+      <c r="D105" t="n">
         <v>2</v>
       </c>
-      <c r="E105">
+      <c r="E105" t="n">
         <v>1</v>
       </c>
       <c r="F105" t="inlineStr">
@@ -8836,7 +8842,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L105">
+      <c r="L105" t="n">
         <v>2014</v>
       </c>
       <c r="M105" t="inlineStr">
@@ -8867,5 +8873,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>